--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124122460</v>
+        <v>124138527</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,48 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436516</v>
+        <v>436655</v>
       </c>
       <c r="R4" t="n">
-        <v>7036958</v>
+        <v>7036737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,26 +952,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -994,28 +965,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138527</v>
+        <v>124138529</v>
       </c>
       <c r="B5" t="n">
         <v>91008</v>
@@ -1055,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436655</v>
+        <v>436661</v>
       </c>
       <c r="R5" t="n">
-        <v>7036737</v>
+        <v>7036719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138529</v>
+        <v>124122460</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,34 +1099,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436661</v>
+        <v>436516</v>
       </c>
       <c r="R6" t="n">
-        <v>7036719</v>
+        <v>7036958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,11 +1170,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1203,26 +1198,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138517</v>
+        <v>124121853</v>
       </c>
       <c r="B7" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,37 +1235,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436623</v>
+        <v>436611</v>
       </c>
       <c r="R7" t="n">
-        <v>7036558</v>
+        <v>7036804</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,11 +1292,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1305,26 +1320,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138535</v>
+        <v>124138517</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>91277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436609</v>
+        <v>436623</v>
       </c>
       <c r="R8" t="n">
-        <v>7036617</v>
+        <v>7036558</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138522</v>
+        <v>124138535</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1479,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436590</v>
+        <v>436609</v>
       </c>
       <c r="R9" t="n">
-        <v>7036784</v>
+        <v>7036617</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1525,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124121853</v>
+        <v>124138522</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,37 +1581,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436611</v>
+        <v>436590</v>
       </c>
       <c r="R10" t="n">
-        <v>7036804</v>
+        <v>7036784</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1598,26 +1638,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1626,41 +1651,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138489</v>
+        <v>124120889</v>
       </c>
       <c r="B15" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,16 +2245,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2263,16 +2263,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436553</v>
+        <v>436483</v>
       </c>
       <c r="R15" t="n">
-        <v>7036719</v>
+        <v>7036812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2302,14 +2307,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,23 +2335,48 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138492</v>
+        <v>124138489</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2376,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436577</v>
+        <v>436553</v>
       </c>
       <c r="R16" t="n">
-        <v>7036686</v>
+        <v>7036719</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2443,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124120889</v>
+        <v>124138518</v>
       </c>
       <c r="B17" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,20 +2495,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2477,21 +2517,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436483</v>
+        <v>436552</v>
       </c>
       <c r="R17" t="n">
-        <v>7036812</v>
+        <v>7036703</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2521,26 +2560,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2549,51 +2573,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138518</v>
+        <v>124138492</v>
       </c>
       <c r="B18" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2602,20 +2601,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2624,20 +2623,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436552</v>
+        <v>436577</v>
       </c>
       <c r="R18" t="n">
-        <v>7036703</v>
+        <v>7036686</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2670,6 +2665,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -5040,10 +5040,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124121048</v>
+        <v>124138500</v>
       </c>
       <c r="B38" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5056,42 +5056,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436428</v>
+        <v>436566</v>
       </c>
       <c r="R38" t="n">
-        <v>7036785</v>
+        <v>7036478</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5118,19 +5113,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5141,51 +5131,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138500</v>
+        <v>124121048</v>
       </c>
       <c r="B39" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5198,37 +5163,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436566</v>
+        <v>436428</v>
       </c>
       <c r="R39" t="n">
-        <v>7036478</v>
+        <v>7036785</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5255,14 +5225,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5273,16 +5248,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138508</v>
+        <v>124121762</v>
       </c>
       <c r="B47" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6112,53 +6112,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436630</v>
+        <v>436547</v>
       </c>
       <c r="R47" t="n">
-        <v>7036552</v>
+        <v>7036757</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6185,11 +6173,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6198,26 +6196,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138490</v>
+        <v>124138508</v>
       </c>
       <c r="B48" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6226,38 +6249,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436542</v>
+        <v>436630</v>
       </c>
       <c r="R48" t="n">
-        <v>7036748</v>
+        <v>7036552</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6290,11 +6325,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6321,10 +6351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124121762</v>
+        <v>124138490</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6337,37 +6367,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436547</v>
+        <v>436542</v>
       </c>
       <c r="R49" t="n">
-        <v>7036757</v>
+        <v>7036748</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6394,19 +6424,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6417,41 +6442,16 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138487</v>
+        <v>124138518</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,38 +789,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436511</v>
+        <v>436552</v>
       </c>
       <c r="R3" t="n">
-        <v>7036406</v>
+        <v>7036703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138527</v>
+        <v>124138505</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436655</v>
+        <v>436515</v>
       </c>
       <c r="R4" t="n">
-        <v>7036737</v>
+        <v>7036414</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138529</v>
+        <v>124138502</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1006,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436661</v>
+        <v>436558</v>
       </c>
       <c r="R5" t="n">
-        <v>7036719</v>
+        <v>7036469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124122460</v>
+        <v>124120678</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,36 +1121,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1137,13 +1150,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436516</v>
+        <v>436489</v>
       </c>
       <c r="R6" t="n">
-        <v>7036958</v>
+        <v>7036772</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1182,12 +1195,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,6 +1215,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1219,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124121853</v>
+        <v>124138490</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,37 +1268,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436611</v>
+        <v>436542</v>
       </c>
       <c r="R7" t="n">
-        <v>7036804</v>
+        <v>7036748</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,24 +1325,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,51 +1343,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138517</v>
+        <v>124121853</v>
       </c>
       <c r="B8" t="n">
-        <v>91277</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,37 +1375,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436623</v>
+        <v>436611</v>
       </c>
       <c r="R8" t="n">
-        <v>7036558</v>
+        <v>7036804</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,11 +1432,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1447,23 +1460,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138535</v>
+        <v>124123595</v>
       </c>
       <c r="B9" t="n">
         <v>78788</v>
@@ -1499,17 +1537,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436609</v>
+        <v>436560</v>
       </c>
       <c r="R9" t="n">
-        <v>7036617</v>
+        <v>7036869</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,11 +1574,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1549,23 +1597,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138522</v>
+        <v>124121048</v>
       </c>
       <c r="B10" t="n">
         <v>91008</v>
@@ -1599,19 +1672,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436590</v>
+        <v>436428</v>
       </c>
       <c r="R10" t="n">
-        <v>7036784</v>
+        <v>7036785</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,11 +1716,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1651,26 +1739,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124124670</v>
+        <v>124138519</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,37 +1796,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436446</v>
+        <v>436513</v>
       </c>
       <c r="R11" t="n">
-        <v>7036676</v>
+        <v>7036741</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,21 +1853,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1763,51 +1866,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124124271</v>
+        <v>124124670</v>
       </c>
       <c r="B12" t="n">
-        <v>91678</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,46 +1894,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436563</v>
+        <v>436446</v>
       </c>
       <c r="R12" t="n">
-        <v>7036748</v>
+        <v>7036676</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1884,7 +1957,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1967,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +2019,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124122388</v>
+        <v>124138492</v>
       </c>
       <c r="B13" t="n">
-        <v>57920</v>
+        <v>57491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,56 +2035,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436519</v>
+        <v>436577</v>
       </c>
       <c r="R13" t="n">
-        <v>7036935</v>
+        <v>7036686</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2038,19 +2092,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:16</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,31 +2110,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124123983</v>
+        <v>124138517</v>
       </c>
       <c r="B14" t="n">
-        <v>57491</v>
+        <v>91277</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,39 +2142,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436575</v>
+        <v>436623</v>
       </c>
       <c r="R14" t="n">
-        <v>7036750</v>
+        <v>7036558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,26 +2199,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2188,51 +2212,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124120889</v>
+        <v>124138529</v>
       </c>
       <c r="B15" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2245,39 +2244,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436483</v>
+        <v>436661</v>
       </c>
       <c r="R15" t="n">
-        <v>7036812</v>
+        <v>7036719</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2307,26 +2301,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2335,48 +2314,23 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138489</v>
+        <v>124123983</v>
       </c>
       <c r="B16" t="n">
         <v>57491</v>
@@ -2410,16 +2364,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436553</v>
+        <v>436575</v>
       </c>
       <c r="R16" t="n">
-        <v>7036719</v>
+        <v>7036750</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,14 +2408,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2467,26 +2436,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138518</v>
+        <v>124138499</v>
       </c>
       <c r="B17" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2495,20 +2489,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2517,20 +2511,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436552</v>
+        <v>436565</v>
       </c>
       <c r="R17" t="n">
-        <v>7036703</v>
+        <v>7036491</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,6 +2553,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,10 +2584,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138492</v>
+        <v>124138521</v>
       </c>
       <c r="B18" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2605,21 +2600,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2629,10 +2624,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436577</v>
+        <v>436548</v>
       </c>
       <c r="R18" t="n">
-        <v>7036686</v>
+        <v>7036699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2665,11 +2660,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2696,10 +2686,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124122264</v>
+        <v>124138494</v>
       </c>
       <c r="B19" t="n">
-        <v>57861</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,20 +2698,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2729,39 +2719,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436515</v>
+        <v>436665</v>
       </c>
       <c r="R19" t="n">
-        <v>7036863</v>
+        <v>7036654</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2793,6 +2764,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2801,31 +2777,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124120703</v>
+        <v>124138535</v>
       </c>
       <c r="B20" t="n">
-        <v>79905</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2834,46 +2805,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436492</v>
+        <v>436609</v>
       </c>
       <c r="R20" t="n">
-        <v>7036774</v>
+        <v>7036617</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2900,26 +2866,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2928,51 +2879,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138499</v>
+        <v>124122264</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>57861</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2981,20 +2907,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3002,20 +2928,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436565</v>
+        <v>436515</v>
       </c>
       <c r="R21" t="n">
-        <v>7036491</v>
+        <v>7036863</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3047,11 +2992,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3060,26 +3000,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124121014</v>
+        <v>124124067</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>90986</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3092,37 +3037,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436440</v>
+        <v>436566</v>
       </c>
       <c r="R22" t="n">
-        <v>7036807</v>
+        <v>7036754</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3151,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3161,7 +3111,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3190,12 +3140,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3213,10 +3163,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124122815</v>
+        <v>124138516</v>
       </c>
       <c r="B23" t="n">
-        <v>56692</v>
+        <v>91435</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3225,51 +3175,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436455</v>
+        <v>436629</v>
       </c>
       <c r="R23" t="n">
-        <v>7036885</v>
+        <v>7036589</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3296,21 +3236,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3319,28 +3249,23 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138531</v>
+        <v>124121014</v>
       </c>
       <c r="B24" t="n">
         <v>78788</v>
@@ -3376,17 +3301,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436554</v>
+        <v>436440</v>
       </c>
       <c r="R24" t="n">
-        <v>7036548</v>
+        <v>7036807</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3413,14 +3338,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3431,26 +3361,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138525</v>
+        <v>124120544</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3463,37 +3418,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436632</v>
+        <v>436449</v>
       </c>
       <c r="R25" t="n">
-        <v>7036740</v>
+        <v>7036726</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3520,11 +3475,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3533,26 +3498,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138516</v>
+        <v>124121762</v>
       </c>
       <c r="B26" t="n">
-        <v>91435</v>
+        <v>78788</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3561,41 +3551,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436629</v>
+        <v>436547</v>
       </c>
       <c r="R26" t="n">
-        <v>7036589</v>
+        <v>7036757</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3622,11 +3612,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3635,26 +3635,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124120467</v>
+        <v>124120889</v>
       </c>
       <c r="B27" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3663,20 +3688,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3684,24 +3709,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3710,13 +3721,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436380</v>
+        <v>436483</v>
       </c>
       <c r="R27" t="n">
-        <v>7036719</v>
+        <v>7036812</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3745,7 +3756,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3755,7 +3766,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3770,6 +3786,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3787,10 +3823,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138521</v>
+        <v>124138514</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>57507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3803,21 +3839,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3827,10 +3863,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436548</v>
+        <v>436467</v>
       </c>
       <c r="R28" t="n">
-        <v>7036699</v>
+        <v>7036669</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3863,6 +3899,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3889,10 +3930,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138497</v>
+        <v>124122426</v>
       </c>
       <c r="B29" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3905,37 +3946,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436619</v>
+        <v>436497</v>
       </c>
       <c r="R29" t="n">
-        <v>7036576</v>
+        <v>7036929</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3962,14 +4003,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,26 +4026,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124122092</v>
+        <v>124138522</v>
       </c>
       <c r="B30" t="n">
-        <v>57644</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4012,53 +4083,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436572</v>
+        <v>436590</v>
       </c>
       <c r="R30" t="n">
-        <v>7036828</v>
+        <v>7036784</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4088,26 +4140,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4116,31 +4153,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138514</v>
+        <v>124138511</v>
       </c>
       <c r="B31" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4153,34 +4185,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436467</v>
+        <v>436582</v>
       </c>
       <c r="R31" t="n">
-        <v>7036669</v>
+        <v>7036714</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4213,11 +4257,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4244,10 +4283,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124119822</v>
+        <v>124123667</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4260,37 +4299,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436287</v>
+        <v>436566</v>
       </c>
       <c r="R32" t="n">
-        <v>7036648</v>
+        <v>7036880</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4317,11 +4361,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4348,12 +4407,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4371,10 +4430,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124123595</v>
+        <v>124122460</v>
       </c>
       <c r="B33" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4387,37 +4446,51 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436560</v>
+        <v>436516</v>
       </c>
       <c r="R33" t="n">
-        <v>7036869</v>
+        <v>7036958</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4446,7 +4519,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4456,7 +4529,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4471,26 +4549,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4508,10 +4566,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124121529</v>
+        <v>124120741</v>
       </c>
       <c r="B34" t="n">
-        <v>57644</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4524,41 +4582,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4567,13 +4611,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436390</v>
+        <v>436483</v>
       </c>
       <c r="R34" t="n">
-        <v>7036767</v>
+        <v>7036788</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4602,7 +4646,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4612,12 +4656,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4632,6 +4671,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4649,10 +4708,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124124067</v>
+        <v>124138524</v>
       </c>
       <c r="B35" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4665,39 +4724,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436566</v>
+        <v>436539</v>
       </c>
       <c r="R35" t="n">
-        <v>7036754</v>
+        <v>7036496</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4727,21 +4781,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4750,51 +4794,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124120678</v>
+        <v>124138534</v>
       </c>
       <c r="B36" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4807,42 +4826,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436489</v>
+        <v>436665</v>
       </c>
       <c r="R36" t="n">
-        <v>7036772</v>
+        <v>7036708</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4869,26 +4883,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4897,51 +4896,26 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138534</v>
+        <v>124138489</v>
       </c>
       <c r="B37" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4954,21 +4928,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4978,10 +4952,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436665</v>
+        <v>436553</v>
       </c>
       <c r="R37" t="n">
-        <v>7036708</v>
+        <v>7036719</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5014,6 +4988,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5040,10 +5019,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138500</v>
+        <v>124122092</v>
       </c>
       <c r="B38" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5056,34 +5035,53 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436566</v>
+        <v>436572</v>
       </c>
       <c r="R38" t="n">
-        <v>7036478</v>
+        <v>7036828</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5113,14 +5111,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5131,23 +5139,28 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124121048</v>
+        <v>124138525</v>
       </c>
       <c r="B39" t="n">
         <v>91008</v>
@@ -5181,24 +5194,19 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436428</v>
+        <v>436632</v>
       </c>
       <c r="R39" t="n">
-        <v>7036785</v>
+        <v>7036740</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5225,21 +5233,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5248,51 +5246,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122426</v>
+        <v>124138500</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5305,37 +5278,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436497</v>
+        <v>436566</v>
       </c>
       <c r="R40" t="n">
-        <v>7036929</v>
+        <v>7036478</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5362,19 +5335,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:17</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5385,51 +5353,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124120741</v>
+        <v>124138508</v>
       </c>
       <c r="B41" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5438,46 +5381,53 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436483</v>
+        <v>436630</v>
       </c>
       <c r="R41" t="n">
-        <v>7036788</v>
+        <v>7036552</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5504,21 +5454,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5527,51 +5467,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138519</v>
+        <v>124121529</v>
       </c>
       <c r="B42" t="n">
-        <v>91008</v>
+        <v>57644</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5584,37 +5499,56 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436513</v>
+        <v>436390</v>
       </c>
       <c r="R42" t="n">
-        <v>7036741</v>
+        <v>7036767</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5641,11 +5575,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5654,26 +5603,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138486</v>
+        <v>124120467</v>
       </c>
       <c r="B43" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5682,41 +5636,60 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436686</v>
+        <v>436380</v>
       </c>
       <c r="R43" t="n">
-        <v>7036815</v>
+        <v>7036719</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5743,11 +5716,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5756,26 +5739,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138494</v>
+        <v>124122388</v>
       </c>
       <c r="B44" t="n">
-        <v>57491</v>
+        <v>57920</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5788,37 +5776,56 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436665</v>
+        <v>436519</v>
       </c>
       <c r="R44" t="n">
-        <v>7036654</v>
+        <v>7036935</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5845,14 +5852,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5863,26 +5875,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138505</v>
+        <v>124138486</v>
       </c>
       <c r="B45" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5895,21 +5912,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5919,10 +5936,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436515</v>
+        <v>436686</v>
       </c>
       <c r="R45" t="n">
-        <v>7036414</v>
+        <v>7036815</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5955,11 +5972,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5986,10 +5998,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138511</v>
+        <v>124120703</v>
       </c>
       <c r="B46" t="n">
-        <v>57644</v>
+        <v>79905</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5998,53 +6010,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436582</v>
+        <v>436492</v>
       </c>
       <c r="R46" t="n">
-        <v>7036714</v>
+        <v>7036774</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6071,11 +6076,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6084,23 +6104,48 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124121762</v>
+        <v>124138531</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -6136,17 +6181,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436547</v>
+        <v>436554</v>
       </c>
       <c r="R47" t="n">
-        <v>7036757</v>
+        <v>7036548</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6173,19 +6218,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6196,51 +6236,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138508</v>
+        <v>124138487</v>
       </c>
       <c r="B48" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6249,50 +6264,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436630</v>
+        <v>436511</v>
       </c>
       <c r="R48" t="n">
-        <v>7036552</v>
+        <v>7036406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6351,7 +6354,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138490</v>
+        <v>124138497</v>
       </c>
       <c r="B49" t="n">
         <v>57491</v>
@@ -6391,10 +6394,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436542</v>
+        <v>436619</v>
       </c>
       <c r="R49" t="n">
-        <v>7036748</v>
+        <v>7036576</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6458,10 +6461,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124120544</v>
+        <v>124124271</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>91678</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6470,41 +6473,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436449</v>
+        <v>436563</v>
       </c>
       <c r="R50" t="n">
-        <v>7036726</v>
+        <v>7036748</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6533,7 +6541,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6543,7 +6551,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6572,12 +6580,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6595,10 +6603,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124123667</v>
+        <v>124122815</v>
       </c>
       <c r="B51" t="n">
-        <v>57507</v>
+        <v>56692</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6611,16 +6619,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6631,7 +6639,12 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6640,13 +6653,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436566</v>
+        <v>436455</v>
       </c>
       <c r="R51" t="n">
-        <v>7036880</v>
+        <v>7036885</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6675,7 +6688,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6685,12 +6698,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6705,26 +6713,6 @@
       <c r="AH51" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6742,7 +6730,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138524</v>
+        <v>124138527</v>
       </c>
       <c r="B52" t="n">
         <v>91008</v>
@@ -6782,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436539</v>
+        <v>436655</v>
       </c>
       <c r="R52" t="n">
-        <v>7036496</v>
+        <v>7036737</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6844,10 +6832,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138502</v>
+        <v>124119822</v>
       </c>
       <c r="B53" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6860,45 +6848,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436558</v>
+        <v>436287</v>
       </c>
       <c r="R53" t="n">
-        <v>7036469</v>
+        <v>7036648</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6930,11 +6910,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6943,16 +6918,41 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138511</v>
+        <v>124121048</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,49 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436582</v>
+        <v>436428</v>
       </c>
       <c r="R2" t="n">
-        <v>7036714</v>
+        <v>7036785</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,11 +753,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -773,26 +776,51 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138525</v>
+        <v>124120703</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>79927</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,41 +829,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436632</v>
+        <v>436492</v>
       </c>
       <c r="R3" t="n">
-        <v>7036740</v>
+        <v>7036774</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,11 +895,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -875,26 +923,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138522</v>
+        <v>124121529</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,37 +980,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436590</v>
+        <v>436390</v>
       </c>
       <c r="R4" t="n">
-        <v>7036784</v>
+        <v>7036767</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,11 +1056,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -977,23 +1084,28 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138492</v>
+        <v>124138489</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1033,10 +1145,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436577</v>
+        <v>436553</v>
       </c>
       <c r="R5" t="n">
-        <v>7036686</v>
+        <v>7036719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1212,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124119822</v>
+        <v>124138535</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1136,17 +1248,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436287</v>
+        <v>436609</v>
       </c>
       <c r="R6" t="n">
-        <v>7036648</v>
+        <v>7036617</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1186,51 +1298,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138534</v>
+        <v>124122815</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,37 +1330,47 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436665</v>
+        <v>436455</v>
       </c>
       <c r="R7" t="n">
-        <v>7036708</v>
+        <v>7036885</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,11 +1397,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1313,26 +1420,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124121529</v>
+        <v>124138490</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,56 +1457,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436390</v>
+        <v>436542</v>
       </c>
       <c r="R8" t="n">
-        <v>7036767</v>
+        <v>7036748</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,24 +1514,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,31 +1532,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138486</v>
+        <v>124123983</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,34 +1564,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436686</v>
+        <v>436575</v>
       </c>
       <c r="R9" t="n">
-        <v>7036815</v>
+        <v>7036750</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,11 +1626,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1556,26 +1654,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124123595</v>
+        <v>124120741</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,37 +1711,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436560</v>
+        <v>436483</v>
       </c>
       <c r="R10" t="n">
-        <v>7036869</v>
+        <v>7036788</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,7 +1775,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1657,7 +1785,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,12 +1814,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1709,10 +1837,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138502</v>
+        <v>124121014</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,45 +1853,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436558</v>
+        <v>436440</v>
       </c>
       <c r="R11" t="n">
-        <v>7036469</v>
+        <v>7036807</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,14 +1910,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,26 +1933,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138487</v>
+        <v>124138524</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1840,21 +1990,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1864,10 +2014,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436511</v>
+        <v>436539</v>
       </c>
       <c r="R12" t="n">
-        <v>7036406</v>
+        <v>7036496</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,10 +2076,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124120889</v>
+        <v>124119822</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,42 +2092,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436483</v>
+        <v>436287</v>
       </c>
       <c r="R13" t="n">
-        <v>7036812</v>
+        <v>7036648</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2004,26 +2149,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2050,12 +2180,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2073,10 +2203,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124121853</v>
+        <v>124138521</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,37 +2219,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436611</v>
+        <v>436548</v>
       </c>
       <c r="R14" t="n">
-        <v>7036804</v>
+        <v>7036699</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,26 +2276,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2174,48 +2289,23 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138489</v>
+        <v>124138505</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2255,10 +2345,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436553</v>
+        <v>436515</v>
       </c>
       <c r="R15" t="n">
-        <v>7036719</v>
+        <v>7036414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2385,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2322,10 +2412,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138499</v>
+        <v>124138486</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,21 +2428,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2362,10 +2452,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436565</v>
+        <v>436686</v>
       </c>
       <c r="R16" t="n">
-        <v>7036491</v>
+        <v>7036815</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,11 +2488,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2514,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138518</v>
+        <v>124124271</v>
       </c>
       <c r="B17" t="n">
-        <v>57883</v>
+        <v>91700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2445,38 +2530,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436552</v>
+        <v>436563</v>
       </c>
       <c r="R17" t="n">
-        <v>7036703</v>
+        <v>7036748</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,11 +2592,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2519,26 +2615,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124120467</v>
+        <v>124138516</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>91457</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2547,60 +2668,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436380</v>
+        <v>436629</v>
       </c>
       <c r="R18" t="n">
-        <v>7036719</v>
+        <v>7036589</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2627,21 +2729,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2650,31 +2742,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124122460</v>
+        <v>124123595</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2687,51 +2774,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436516</v>
+        <v>436560</v>
       </c>
       <c r="R19" t="n">
-        <v>7036958</v>
+        <v>7036869</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2760,7 +2833,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2770,12 +2843,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,6 +2858,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2807,10 +2895,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124123667</v>
+        <v>124124670</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,42 +2911,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436566</v>
+        <v>436446</v>
       </c>
       <c r="R20" t="n">
-        <v>7036880</v>
+        <v>7036676</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2887,7 +2970,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2897,12 +2980,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2931,12 +3009,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2954,10 +3032,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138490</v>
+        <v>124120889</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2970,16 +3048,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2988,16 +3066,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436542</v>
+        <v>436483</v>
       </c>
       <c r="R21" t="n">
-        <v>7036748</v>
+        <v>7036812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3027,14 +3110,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,26 +3138,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124120703</v>
+        <v>124122426</v>
       </c>
       <c r="B22" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3073,43 +3191,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436492</v>
+        <v>436497</v>
       </c>
       <c r="R22" t="n">
-        <v>7036774</v>
+        <v>7036929</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3141,7 +3254,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3151,12 +3264,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,22 +3283,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3208,10 +3316,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124124670</v>
+        <v>124138527</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3224,37 +3332,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436446</v>
+        <v>436655</v>
       </c>
       <c r="R23" t="n">
-        <v>7036676</v>
+        <v>7036737</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3281,21 +3389,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3304,51 +3402,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138535</v>
+        <v>124122460</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3361,34 +3434,48 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436609</v>
+        <v>436516</v>
       </c>
       <c r="R24" t="n">
-        <v>7036617</v>
+        <v>7036958</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3418,11 +3505,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3431,26 +3533,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138494</v>
+        <v>124138518</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3459,20 +3566,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3481,16 +3588,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436665</v>
+        <v>436552</v>
       </c>
       <c r="R25" t="n">
-        <v>7036654</v>
+        <v>7036703</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3523,11 +3634,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3554,10 +3660,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138497</v>
+        <v>124122388</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>57942</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3570,37 +3676,56 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436619</v>
+        <v>436519</v>
       </c>
       <c r="R26" t="n">
-        <v>7036576</v>
+        <v>7036935</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3627,14 +3752,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,26 +3775,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138517</v>
+        <v>124138499</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3677,21 +3812,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3701,10 +3836,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436623</v>
+        <v>436565</v>
       </c>
       <c r="R27" t="n">
-        <v>7036558</v>
+        <v>7036491</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3737,6 +3872,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3763,10 +3903,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138508</v>
+        <v>124120678</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>79892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3775,53 +3915,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436630</v>
+        <v>436489</v>
       </c>
       <c r="R28" t="n">
-        <v>7036552</v>
+        <v>7036772</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3848,11 +3981,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3861,26 +4009,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138484</v>
+        <v>124121853</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3893,37 +4066,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436524</v>
+        <v>436611</v>
       </c>
       <c r="R29" t="n">
-        <v>7036571</v>
+        <v>7036804</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3950,11 +4123,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3963,26 +4151,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138516</v>
+        <v>124138529</v>
       </c>
       <c r="B30" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3991,25 +4204,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4019,10 +4232,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436629</v>
+        <v>436661</v>
       </c>
       <c r="R30" t="n">
-        <v>7036589</v>
+        <v>7036719</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4081,10 +4294,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138529</v>
+        <v>124138511</v>
       </c>
       <c r="B31" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4097,34 +4310,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436661</v>
+        <v>436582</v>
       </c>
       <c r="R31" t="n">
-        <v>7036719</v>
+        <v>7036714</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4183,10 +4408,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124120544</v>
+        <v>124138494</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4199,37 +4424,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436449</v>
+        <v>436665</v>
       </c>
       <c r="R32" t="n">
-        <v>7036726</v>
+        <v>7036654</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4256,19 +4481,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4279,51 +4499,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124120741</v>
+        <v>124138497</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4336,42 +4531,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436483</v>
+        <v>436619</v>
       </c>
       <c r="R33" t="n">
-        <v>7036788</v>
+        <v>7036576</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4398,19 +4588,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:26</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4421,51 +4606,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124122264</v>
+        <v>124124067</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4474,45 +4634,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4521,13 +4667,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436515</v>
+        <v>436566</v>
       </c>
       <c r="R34" t="n">
-        <v>7036863</v>
+        <v>7036754</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4554,11 +4700,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4571,6 +4727,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4588,7 +4764,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138519</v>
+        <v>124138525</v>
       </c>
       <c r="B35" t="n">
         <v>91030</v>
@@ -4628,10 +4804,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436513</v>
+        <v>436632</v>
       </c>
       <c r="R35" t="n">
-        <v>7036741</v>
+        <v>7036740</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4690,10 +4866,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138505</v>
+        <v>124120544</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4706,37 +4882,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436515</v>
+        <v>436449</v>
       </c>
       <c r="R36" t="n">
-        <v>7036414</v>
+        <v>7036726</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4763,14 +4939,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4781,26 +4962,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124122092</v>
+        <v>124121762</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,56 +5019,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436572</v>
+        <v>436547</v>
       </c>
       <c r="R37" t="n">
-        <v>7036828</v>
+        <v>7036757</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4891,7 +5078,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4901,12 +5088,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4921,6 +5103,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4938,10 +5140,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124122388</v>
+        <v>124138522</v>
       </c>
       <c r="B38" t="n">
-        <v>57942</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4954,56 +5156,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436519</v>
+        <v>436590</v>
       </c>
       <c r="R38" t="n">
-        <v>7036935</v>
+        <v>7036784</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5030,21 +5213,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5053,31 +5226,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124121048</v>
+        <v>124138502</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5090,42 +5258,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436428</v>
+        <v>436558</v>
       </c>
       <c r="R39" t="n">
-        <v>7036785</v>
+        <v>7036469</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5152,19 +5323,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5175,51 +5341,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122426</v>
+        <v>124138492</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5232,37 +5373,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436497</v>
+        <v>436577</v>
       </c>
       <c r="R40" t="n">
-        <v>7036929</v>
+        <v>7036686</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5289,19 +5430,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:17</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5312,51 +5448,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124122815</v>
+        <v>124138484</v>
       </c>
       <c r="B41" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5369,47 +5480,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436455</v>
+        <v>436524</v>
       </c>
       <c r="R41" t="n">
-        <v>7036885</v>
+        <v>7036571</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5436,21 +5537,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5459,31 +5550,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138527</v>
+        <v>124138508</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5492,38 +5578,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436655</v>
+        <v>436630</v>
       </c>
       <c r="R42" t="n">
-        <v>7036737</v>
+        <v>7036552</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5582,10 +5680,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138524</v>
+        <v>124138534</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5598,21 +5696,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5622,10 +5720,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436539</v>
+        <v>436665</v>
       </c>
       <c r="R43" t="n">
-        <v>7036496</v>
+        <v>7036708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5684,10 +5782,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138521</v>
+        <v>124138514</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5700,21 +5798,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5724,10 +5822,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436548</v>
+        <v>436467</v>
       </c>
       <c r="R44" t="n">
-        <v>7036699</v>
+        <v>7036669</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5760,6 +5858,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5786,10 +5889,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124121762</v>
+        <v>124138517</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5802,37 +5905,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436547</v>
+        <v>436623</v>
       </c>
       <c r="R45" t="n">
-        <v>7036757</v>
+        <v>7036558</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5859,21 +5962,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5882,51 +5975,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138500</v>
+        <v>124123667</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5939,16 +6007,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5957,19 +6025,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>436566</v>
       </c>
       <c r="R46" t="n">
-        <v>7036478</v>
+        <v>7036880</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5996,14 +6069,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6014,26 +6097,51 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138514</v>
+        <v>124138500</v>
       </c>
       <c r="B47" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6046,16 +6154,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6070,10 +6178,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436467</v>
+        <v>436566</v>
       </c>
       <c r="R47" t="n">
-        <v>7036669</v>
+        <v>7036478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6110,7 +6218,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Hack äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6137,10 +6245,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124123983</v>
+        <v>124138519</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6153,39 +6261,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436575</v>
+        <v>436513</v>
       </c>
       <c r="R48" t="n">
-        <v>7036750</v>
+        <v>7036741</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6215,26 +6318,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6243,51 +6331,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124120678</v>
+        <v>124138531</v>
       </c>
       <c r="B49" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6300,42 +6363,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436489</v>
+        <v>436554</v>
       </c>
       <c r="R49" t="n">
-        <v>7036772</v>
+        <v>7036548</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6362,24 +6420,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6390,51 +6438,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124124067</v>
+        <v>124122264</v>
       </c>
       <c r="B50" t="n">
-        <v>91008</v>
+        <v>57883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6443,31 +6466,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6476,13 +6513,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436566</v>
+        <v>436515</v>
       </c>
       <c r="R50" t="n">
-        <v>7036754</v>
+        <v>7036863</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6509,21 +6546,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6536,26 +6563,6 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6573,10 +6580,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124121014</v>
+        <v>124138487</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6589,37 +6596,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436440</v>
+        <v>436511</v>
       </c>
       <c r="R51" t="n">
-        <v>7036807</v>
+        <v>7036406</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6646,21 +6653,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6669,51 +6666,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138531</v>
+        <v>124122092</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6726,34 +6698,53 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436554</v>
+        <v>436572</v>
       </c>
       <c r="R52" t="n">
-        <v>7036548</v>
+        <v>7036828</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6783,14 +6774,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6801,26 +6802,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124124271</v>
+        <v>124120467</v>
       </c>
       <c r="B53" t="n">
-        <v>91700</v>
+        <v>57883</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6833,27 +6839,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3298</v>
+        <v>103015</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6862,13 +6882,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436563</v>
+        <v>436380</v>
       </c>
       <c r="R53" t="n">
-        <v>7036748</v>
+        <v>7036719</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6897,7 +6917,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6907,7 +6927,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6922,26 +6942,6 @@
       <c r="AH53" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124121048</v>
+        <v>124138499</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436428</v>
+        <v>436565</v>
       </c>
       <c r="R2" t="n">
-        <v>7036785</v>
+        <v>7036491</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,19 +748,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,51 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124120703</v>
+        <v>124121048</v>
       </c>
       <c r="B3" t="n">
-        <v>79927</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -829,31 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -862,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436492</v>
+        <v>436428</v>
       </c>
       <c r="R3" t="n">
-        <v>7036774</v>
+        <v>7036785</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -931,22 +891,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124121529</v>
+        <v>124122426</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -980,56 +940,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436390</v>
+        <v>436497</v>
       </c>
       <c r="R4" t="n">
-        <v>7036767</v>
+        <v>7036929</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1058,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1068,12 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,6 +1024,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1105,10 +1061,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138489</v>
+        <v>124123667</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1121,16 +1077,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1139,19 +1095,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436553</v>
+        <v>436566</v>
       </c>
       <c r="R5" t="n">
-        <v>7036719</v>
+        <v>7036880</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1178,14 +1139,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1196,26 +1167,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138535</v>
+        <v>124120889</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1228,34 +1224,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436609</v>
+        <v>436483</v>
       </c>
       <c r="R6" t="n">
-        <v>7036617</v>
+        <v>7036812</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,11 +1286,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1298,26 +1314,51 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124122815</v>
+        <v>124121853</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1330,47 +1371,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436455</v>
+        <v>436611</v>
       </c>
       <c r="R7" t="n">
-        <v>7036885</v>
+        <v>7036804</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1399,7 +1430,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1409,7 +1440,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,6 +1460,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1441,10 +1497,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138490</v>
+        <v>124138517</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,21 +1513,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1537,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436542</v>
+        <v>436623</v>
       </c>
       <c r="R8" t="n">
-        <v>7036748</v>
+        <v>7036558</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1517,11 +1573,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123983</v>
+        <v>124138514</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1564,16 +1615,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1582,21 +1633,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436575</v>
+        <v>436467</v>
       </c>
       <c r="R9" t="n">
-        <v>7036750</v>
+        <v>7036669</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,24 +1672,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,51 +1690,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124120741</v>
+        <v>124138531</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,42 +1722,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436483</v>
+        <v>436554</v>
       </c>
       <c r="R10" t="n">
-        <v>7036788</v>
+        <v>7036548</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1773,19 +1779,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:26</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1796,51 +1797,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124121014</v>
+        <v>124138492</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1853,37 +1829,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436440</v>
+        <v>436577</v>
       </c>
       <c r="R11" t="n">
-        <v>7036807</v>
+        <v>7036686</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1910,19 +1886,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1933,51 +1904,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138524</v>
+        <v>124120544</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1990,37 +1936,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436539</v>
+        <v>436449</v>
       </c>
       <c r="R12" t="n">
-        <v>7036496</v>
+        <v>7036726</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2047,11 +1993,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2060,26 +2016,51 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124119822</v>
+        <v>124123983</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2092,37 +2073,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436287</v>
+        <v>436575</v>
       </c>
       <c r="R13" t="n">
-        <v>7036648</v>
+        <v>7036750</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2149,11 +2135,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2180,12 +2181,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2203,10 +2204,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138521</v>
+        <v>124121014</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2219,37 +2220,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436548</v>
+        <v>436440</v>
       </c>
       <c r="R14" t="n">
-        <v>7036699</v>
+        <v>7036807</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2276,11 +2277,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2289,26 +2300,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138505</v>
+        <v>124138535</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2321,21 +2357,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2345,10 +2381,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436515</v>
+        <v>436609</v>
       </c>
       <c r="R15" t="n">
-        <v>7036414</v>
+        <v>7036617</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2381,11 +2417,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2412,10 +2443,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138486</v>
+        <v>124138525</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2428,21 +2459,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2452,10 +2483,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436686</v>
+        <v>436632</v>
       </c>
       <c r="R16" t="n">
-        <v>7036815</v>
+        <v>7036740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2514,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124124271</v>
+        <v>124121762</v>
       </c>
       <c r="B17" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2526,46 +2557,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436563</v>
+        <v>436547</v>
       </c>
       <c r="R17" t="n">
-        <v>7036748</v>
+        <v>7036757</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2594,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2604,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2633,12 +2659,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2656,10 +2682,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138516</v>
+        <v>124121529</v>
       </c>
       <c r="B18" t="n">
-        <v>91457</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2668,41 +2694,60 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436629</v>
+        <v>436390</v>
       </c>
       <c r="R18" t="n">
-        <v>7036589</v>
+        <v>7036767</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2729,11 +2774,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2742,26 +2802,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124123595</v>
+        <v>124138500</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2774,37 +2839,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436560</v>
+        <v>436566</v>
       </c>
       <c r="R19" t="n">
-        <v>7036869</v>
+        <v>7036478</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2831,19 +2896,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:51</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,51 +2914,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124124670</v>
+        <v>124138527</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2911,37 +2946,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436446</v>
+        <v>436655</v>
       </c>
       <c r="R20" t="n">
-        <v>7036676</v>
+        <v>7036737</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2968,21 +3003,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2991,51 +3016,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124120889</v>
+        <v>124124271</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>91700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3044,31 +3044,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3077,10 +3077,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436483</v>
+        <v>436563</v>
       </c>
       <c r="R21" t="n">
-        <v>7036812</v>
+        <v>7036748</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3122,12 +3122,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,12 +3151,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3179,10 +3174,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124122426</v>
+        <v>124122815</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3195,34 +3190,44 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436497</v>
+        <v>436455</v>
       </c>
       <c r="R22" t="n">
-        <v>7036929</v>
+        <v>7036885</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -3254,7 +3259,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3264,7 +3269,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3279,26 +3284,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3316,10 +3301,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138527</v>
+        <v>124138534</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3332,21 +3317,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3356,10 +3341,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436655</v>
+        <v>436665</v>
       </c>
       <c r="R23" t="n">
-        <v>7036737</v>
+        <v>7036708</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3418,10 +3403,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124122460</v>
+        <v>124138490</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3434,48 +3419,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436516</v>
+        <v>436542</v>
       </c>
       <c r="R24" t="n">
-        <v>7036958</v>
+        <v>7036748</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3505,24 +3476,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3533,21 +3494,16 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3660,10 +3616,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124122388</v>
+        <v>124122264</v>
       </c>
       <c r="B26" t="n">
-        <v>57942</v>
+        <v>57883</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3672,25 +3628,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103001</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3719,13 +3675,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436519</v>
+        <v>436515</v>
       </c>
       <c r="R26" t="n">
-        <v>7036935</v>
+        <v>7036863</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3752,19 +3708,9 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3796,10 +3742,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138499</v>
+        <v>124138521</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3812,21 +3758,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3836,10 +3782,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436565</v>
+        <v>436548</v>
       </c>
       <c r="R27" t="n">
-        <v>7036491</v>
+        <v>7036699</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3872,11 +3818,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3903,10 +3844,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124120678</v>
+        <v>124138494</v>
       </c>
       <c r="B28" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3919,42 +3860,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436489</v>
+        <v>436665</v>
       </c>
       <c r="R28" t="n">
-        <v>7036772</v>
+        <v>7036654</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3981,24 +3917,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4009,51 +3935,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124121853</v>
+        <v>124138486</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4066,37 +3967,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436611</v>
+        <v>436686</v>
       </c>
       <c r="R29" t="n">
-        <v>7036804</v>
+        <v>7036815</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4123,26 +4024,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4151,51 +4037,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138529</v>
+        <v>124124067</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4208,34 +4069,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436661</v>
+        <v>436566</v>
       </c>
       <c r="R30" t="n">
-        <v>7036719</v>
+        <v>7036754</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4265,11 +4131,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4278,26 +4154,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138511</v>
+        <v>124120703</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4306,53 +4207,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436582</v>
+        <v>436492</v>
       </c>
       <c r="R31" t="n">
-        <v>7036714</v>
+        <v>7036774</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4379,11 +4273,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4392,26 +4301,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138494</v>
+        <v>124138508</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4420,38 +4354,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436665</v>
+        <v>436630</v>
       </c>
       <c r="R32" t="n">
-        <v>7036654</v>
+        <v>7036552</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4484,11 +4430,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4515,10 +4456,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138497</v>
+        <v>124138487</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4531,21 +4472,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4555,10 +4496,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436619</v>
+        <v>436511</v>
       </c>
       <c r="R33" t="n">
-        <v>7036576</v>
+        <v>7036406</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4591,11 +4532,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4622,10 +4558,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124124067</v>
+        <v>124138505</v>
       </c>
       <c r="B34" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4638,39 +4574,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436566</v>
+        <v>436515</v>
       </c>
       <c r="R34" t="n">
-        <v>7036754</v>
+        <v>7036414</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4700,19 +4631,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:03</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4723,48 +4649,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138525</v>
+        <v>124138519</v>
       </c>
       <c r="B35" t="n">
         <v>91030</v>
@@ -4804,10 +4705,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436632</v>
+        <v>436513</v>
       </c>
       <c r="R35" t="n">
-        <v>7036740</v>
+        <v>7036741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4866,7 +4767,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124120544</v>
+        <v>124123595</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4906,13 +4807,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436449</v>
+        <v>436560</v>
       </c>
       <c r="R36" t="n">
-        <v>7036726</v>
+        <v>7036869</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4941,7 +4842,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4951,7 +4852,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5003,10 +4904,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124121762</v>
+        <v>124138524</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5019,37 +4920,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436547</v>
+        <v>436539</v>
       </c>
       <c r="R37" t="n">
-        <v>7036757</v>
+        <v>7036496</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5076,21 +4977,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5099,51 +4990,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138522</v>
+        <v>124138489</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5156,21 +5022,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5180,10 +5046,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436590</v>
+        <v>436553</v>
       </c>
       <c r="R38" t="n">
-        <v>7036784</v>
+        <v>7036719</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5216,6 +5082,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5242,10 +5113,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138502</v>
+        <v>124120467</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5254,20 +5125,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5275,28 +5146,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436558</v>
+        <v>436380</v>
       </c>
       <c r="R39" t="n">
-        <v>7036469</v>
+        <v>7036719</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5323,14 +5205,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5341,26 +5228,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124138492</v>
+        <v>124122460</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5373,34 +5265,48 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436577</v>
+        <v>436516</v>
       </c>
       <c r="R40" t="n">
-        <v>7036686</v>
+        <v>7036958</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5430,14 +5336,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5448,26 +5364,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138484</v>
+        <v>124138511</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5480,34 +5401,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436524</v>
+        <v>436582</v>
       </c>
       <c r="R41" t="n">
-        <v>7036571</v>
+        <v>7036714</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5566,10 +5499,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138508</v>
+        <v>124138484</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5578,50 +5511,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436630</v>
+        <v>436524</v>
       </c>
       <c r="R42" t="n">
-        <v>7036552</v>
+        <v>7036571</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5680,10 +5601,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138534</v>
+        <v>124138522</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5696,21 +5617,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5720,10 +5641,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436665</v>
+        <v>436590</v>
       </c>
       <c r="R43" t="n">
-        <v>7036708</v>
+        <v>7036784</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5782,10 +5703,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138514</v>
+        <v>124138502</v>
       </c>
       <c r="B44" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5798,16 +5719,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5816,16 +5737,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436467</v>
+        <v>436558</v>
       </c>
       <c r="R44" t="n">
-        <v>7036669</v>
+        <v>7036469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5862,7 +5791,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Hack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5889,10 +5818,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138517</v>
+        <v>124138497</v>
       </c>
       <c r="B45" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5905,21 +5834,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5929,10 +5858,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436623</v>
+        <v>436619</v>
       </c>
       <c r="R45" t="n">
-        <v>7036558</v>
+        <v>7036576</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5965,6 +5894,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5991,10 +5925,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124123667</v>
+        <v>124120741</v>
       </c>
       <c r="B46" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6007,27 +5941,27 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6036,13 +5970,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436566</v>
+        <v>436483</v>
       </c>
       <c r="R46" t="n">
-        <v>7036880</v>
+        <v>7036788</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6071,7 +6005,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6081,12 +6015,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6115,12 +6044,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6138,10 +6067,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138500</v>
+        <v>124138529</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6154,21 +6083,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6178,10 +6107,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436566</v>
+        <v>436661</v>
       </c>
       <c r="R47" t="n">
-        <v>7036478</v>
+        <v>7036719</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6214,11 +6143,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6245,10 +6169,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138519</v>
+        <v>124120678</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6261,37 +6185,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436513</v>
+        <v>436489</v>
       </c>
       <c r="R48" t="n">
-        <v>7036741</v>
+        <v>7036772</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6318,11 +6247,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6331,23 +6275,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138531</v>
+        <v>124124670</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -6383,17 +6352,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436554</v>
+        <v>436446</v>
       </c>
       <c r="R49" t="n">
-        <v>7036548</v>
+        <v>7036676</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6420,14 +6389,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6438,26 +6412,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124122264</v>
+        <v>124122388</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>57942</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6466,25 +6465,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6513,13 +6512,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436515</v>
+        <v>436519</v>
       </c>
       <c r="R50" t="n">
-        <v>7036863</v>
+        <v>7036935</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6546,9 +6545,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6580,10 +6589,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138487</v>
+        <v>124119822</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6596,37 +6605,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436511</v>
+        <v>436287</v>
       </c>
       <c r="R51" t="n">
-        <v>7036406</v>
+        <v>7036648</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6666,26 +6675,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124122092</v>
+        <v>124138516</v>
       </c>
       <c r="B52" t="n">
-        <v>57666</v>
+        <v>91457</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6694,57 +6728,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436572</v>
+        <v>436629</v>
       </c>
       <c r="R52" t="n">
-        <v>7036828</v>
+        <v>7036589</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6774,26 +6789,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6802,31 +6802,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124120467</v>
+        <v>124122092</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6835,25 +6830,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6882,13 +6877,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436380</v>
+        <v>436572</v>
       </c>
       <c r="R53" t="n">
-        <v>7036719</v>
+        <v>7036828</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6917,7 +6912,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6927,7 +6922,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138499</v>
+        <v>124138522</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436565</v>
+        <v>436590</v>
       </c>
       <c r="R2" t="n">
-        <v>7036491</v>
+        <v>7036784</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124121048</v>
+        <v>124138490</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436428</v>
+        <v>436542</v>
       </c>
       <c r="R3" t="n">
-        <v>7036785</v>
+        <v>7036748</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +850,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,51 +868,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124122426</v>
+        <v>124138511</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,37 +900,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436497</v>
+        <v>436582</v>
       </c>
       <c r="R4" t="n">
-        <v>7036929</v>
+        <v>7036714</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,21 +969,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,51 +982,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124123667</v>
+        <v>124138516</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91457</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,46 +1010,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436566</v>
+        <v>436629</v>
       </c>
       <c r="R5" t="n">
-        <v>7036880</v>
+        <v>7036589</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1139,26 +1071,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1167,51 +1084,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124120889</v>
+        <v>124138527</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1224,39 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436483</v>
+        <v>436655</v>
       </c>
       <c r="R6" t="n">
-        <v>7036812</v>
+        <v>7036737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1286,26 +1173,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1314,51 +1186,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124121853</v>
+        <v>124138529</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1371,37 +1218,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436611</v>
+        <v>436661</v>
       </c>
       <c r="R7" t="n">
-        <v>7036804</v>
+        <v>7036719</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1428,26 +1275,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1456,51 +1288,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138517</v>
+        <v>124138500</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1513,21 +1320,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1537,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436623</v>
+        <v>436566</v>
       </c>
       <c r="R8" t="n">
-        <v>7036558</v>
+        <v>7036478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1573,6 +1380,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1599,10 +1411,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138514</v>
+        <v>124120703</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>79927</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,41 +1423,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436467</v>
+        <v>436492</v>
       </c>
       <c r="R9" t="n">
-        <v>7036669</v>
+        <v>7036774</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1672,14 +1489,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack äldre</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1690,23 +1517,48 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138531</v>
+        <v>124121853</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1742,17 +1594,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436554</v>
+        <v>436611</v>
       </c>
       <c r="R10" t="n">
-        <v>7036548</v>
+        <v>7036804</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1779,14 +1631,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1797,26 +1659,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138492</v>
+        <v>124120741</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1829,37 +1716,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436577</v>
+        <v>436483</v>
       </c>
       <c r="R11" t="n">
-        <v>7036686</v>
+        <v>7036788</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1886,14 +1778,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,26 +1801,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124120544</v>
+        <v>124120678</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1936,34 +1858,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436449</v>
+        <v>436489</v>
       </c>
       <c r="R12" t="n">
-        <v>7036726</v>
+        <v>7036772</v>
       </c>
       <c r="S12" t="n">
         <v>7</v>
@@ -1995,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2005,7 +1932,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,22 +1956,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2057,10 +1989,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124123983</v>
+        <v>124122460</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2073,27 +2005,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2102,10 +2043,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436575</v>
+        <v>436516</v>
       </c>
       <c r="R13" t="n">
-        <v>7036750</v>
+        <v>7036958</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2137,7 +2078,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2147,12 +2088,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2167,26 +2108,6 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2204,10 +2125,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124121014</v>
+        <v>124138508</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2216,41 +2137,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436440</v>
+        <v>436630</v>
       </c>
       <c r="R14" t="n">
-        <v>7036807</v>
+        <v>7036552</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2277,21 +2210,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2300,51 +2223,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138535</v>
+        <v>124138517</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2357,21 +2255,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2381,10 +2279,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436609</v>
+        <v>436623</v>
       </c>
       <c r="R15" t="n">
-        <v>7036617</v>
+        <v>7036558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2443,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138525</v>
+        <v>124122815</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2459,37 +2357,47 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436632</v>
+        <v>436455</v>
       </c>
       <c r="R16" t="n">
-        <v>7036740</v>
+        <v>7036885</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2516,11 +2424,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2529,26 +2447,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124121762</v>
+        <v>124138484</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2561,37 +2484,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436547</v>
+        <v>436524</v>
       </c>
       <c r="R17" t="n">
-        <v>7036757</v>
+        <v>7036571</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2618,21 +2541,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2641,51 +2554,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124121529</v>
+        <v>124138525</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2698,56 +2586,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436390</v>
+        <v>436632</v>
       </c>
       <c r="R18" t="n">
-        <v>7036767</v>
+        <v>7036740</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2774,26 +2643,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2802,28 +2656,23 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138500</v>
+        <v>124138494</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2863,10 +2712,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436566</v>
+        <v>436665</v>
       </c>
       <c r="R19" t="n">
-        <v>7036478</v>
+        <v>7036654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2903,7 +2752,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2930,10 +2779,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138527</v>
+        <v>124138492</v>
       </c>
       <c r="B20" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2946,21 +2795,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2970,10 +2819,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436655</v>
+        <v>436577</v>
       </c>
       <c r="R20" t="n">
-        <v>7036737</v>
+        <v>7036686</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3006,6 +2855,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3032,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124124271</v>
+        <v>124124670</v>
       </c>
       <c r="B21" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3044,46 +2898,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436563</v>
+        <v>436446</v>
       </c>
       <c r="R21" t="n">
-        <v>7036748</v>
+        <v>7036676</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3112,7 +2961,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3122,7 +2971,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3174,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124122815</v>
+        <v>124138518</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>57883</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3186,20 +3035,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3208,29 +3057,23 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436455</v>
+        <v>436552</v>
       </c>
       <c r="R22" t="n">
-        <v>7036885</v>
+        <v>7036703</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3257,21 +3100,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3280,31 +3113,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138534</v>
+        <v>124138489</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3317,21 +3145,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3341,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436665</v>
+        <v>436553</v>
       </c>
       <c r="R23" t="n">
-        <v>7036708</v>
+        <v>7036719</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3377,6 +3205,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3236,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138490</v>
+        <v>124121014</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3419,37 +3252,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436542</v>
+        <v>436440</v>
       </c>
       <c r="R24" t="n">
-        <v>7036748</v>
+        <v>7036807</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3476,14 +3309,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3494,23 +3332,48 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138518</v>
+        <v>124122264</v>
       </c>
       <c r="B25" t="n">
         <v>57883</v>
@@ -3543,24 +3406,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436552</v>
+        <v>436515</v>
       </c>
       <c r="R25" t="n">
-        <v>7036703</v>
+        <v>7036863</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3600,26 +3478,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124122264</v>
+        <v>124121762</v>
       </c>
       <c r="B26" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3628,60 +3511,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436515</v>
+        <v>436547</v>
       </c>
       <c r="R26" t="n">
-        <v>7036863</v>
+        <v>7036757</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3708,11 +3572,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3725,6 +3599,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3742,10 +3636,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138521</v>
+        <v>124124067</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3758,34 +3652,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436548</v>
+        <v>436566</v>
       </c>
       <c r="R27" t="n">
-        <v>7036699</v>
+        <v>7036754</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3815,11 +3714,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3828,26 +3737,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138494</v>
+        <v>124138487</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3860,21 +3794,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3884,10 +3818,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436665</v>
+        <v>436511</v>
       </c>
       <c r="R28" t="n">
-        <v>7036654</v>
+        <v>7036406</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3920,11 +3854,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,10 +3880,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138486</v>
+        <v>124122426</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3967,37 +3896,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436686</v>
+        <v>436497</v>
       </c>
       <c r="R29" t="n">
-        <v>7036815</v>
+        <v>7036929</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4024,11 +3953,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4037,26 +3976,51 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124124067</v>
+        <v>124123983</v>
       </c>
       <c r="B30" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4069,27 +4033,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4098,10 +4062,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436566</v>
+        <v>436575</v>
       </c>
       <c r="R30" t="n">
-        <v>7036754</v>
+        <v>7036750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4133,7 +4097,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4143,7 +4107,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4195,10 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124120703</v>
+        <v>124120544</v>
       </c>
       <c r="B31" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4207,46 +4176,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436492</v>
+        <v>436449</v>
       </c>
       <c r="R31" t="n">
-        <v>7036774</v>
+        <v>7036726</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4275,7 +4239,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4285,12 +4249,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4309,22 +4268,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4342,10 +4301,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138508</v>
+        <v>124138531</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4354,50 +4313,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436630</v>
+        <v>436554</v>
       </c>
       <c r="R32" t="n">
-        <v>7036552</v>
+        <v>7036548</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4430,6 +4377,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4456,10 +4408,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138487</v>
+        <v>124119822</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4472,37 +4424,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436511</v>
+        <v>436287</v>
       </c>
       <c r="R33" t="n">
-        <v>7036406</v>
+        <v>7036648</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4542,26 +4494,51 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138505</v>
+        <v>124124271</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4570,38 +4547,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436515</v>
+        <v>436563</v>
       </c>
       <c r="R34" t="n">
-        <v>7036414</v>
+        <v>7036748</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4631,14 +4613,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4649,23 +4636,48 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138519</v>
+        <v>124138521</v>
       </c>
       <c r="B35" t="n">
         <v>91030</v>
@@ -4705,10 +4717,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436513</v>
+        <v>436548</v>
       </c>
       <c r="R35" t="n">
-        <v>7036741</v>
+        <v>7036699</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4767,10 +4779,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124123595</v>
+        <v>124138514</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4783,37 +4795,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436560</v>
+        <v>436467</v>
       </c>
       <c r="R36" t="n">
-        <v>7036869</v>
+        <v>7036669</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4840,19 +4852,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:51</t>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4863,48 +4870,23 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138524</v>
+        <v>124121048</v>
       </c>
       <c r="B37" t="n">
         <v>91030</v>
@@ -4938,19 +4920,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436539</v>
+        <v>436428</v>
       </c>
       <c r="R37" t="n">
-        <v>7036496</v>
+        <v>7036785</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4977,11 +4964,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4990,23 +4987,48 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138489</v>
+        <v>124138497</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -5046,10 +5068,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436553</v>
+        <v>436619</v>
       </c>
       <c r="R38" t="n">
-        <v>7036719</v>
+        <v>7036576</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5113,10 +5135,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124120467</v>
+        <v>124138534</v>
       </c>
       <c r="B39" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5125,60 +5147,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436380</v>
+        <v>436665</v>
       </c>
       <c r="R39" t="n">
-        <v>7036719</v>
+        <v>7036708</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5205,21 +5208,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5228,31 +5221,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122460</v>
+        <v>124122388</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5265,21 +5253,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5287,9 +5275,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5303,13 +5296,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436516</v>
+        <v>436519</v>
       </c>
       <c r="R40" t="n">
-        <v>7036958</v>
+        <v>7036935</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5338,7 +5331,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5348,12 +5341,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5385,10 +5373,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138511</v>
+        <v>124123667</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5401,49 +5389,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436582</v>
+        <v>436566</v>
       </c>
       <c r="R41" t="n">
-        <v>7036714</v>
+        <v>7036880</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5470,11 +5451,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5483,26 +5479,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138484</v>
+        <v>124123595</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5515,37 +5536,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436524</v>
+        <v>436560</v>
       </c>
       <c r="R42" t="n">
-        <v>7036571</v>
+        <v>7036869</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5572,11 +5593,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5585,26 +5616,51 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138522</v>
+        <v>124122092</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5617,34 +5673,53 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436590</v>
+        <v>436572</v>
       </c>
       <c r="R43" t="n">
-        <v>7036784</v>
+        <v>7036828</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5674,11 +5749,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5687,26 +5777,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138502</v>
+        <v>124120467</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5715,20 +5810,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5736,28 +5831,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436558</v>
+        <v>436380</v>
       </c>
       <c r="R44" t="n">
-        <v>7036469</v>
+        <v>7036719</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5784,14 +5890,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5802,23 +5913,28 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138497</v>
+        <v>124138502</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5852,16 +5968,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436619</v>
+        <v>436558</v>
       </c>
       <c r="R45" t="n">
-        <v>7036576</v>
+        <v>7036469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5898,7 +6022,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5925,10 +6049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124120741</v>
+        <v>124138486</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5941,42 +6065,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436483</v>
+        <v>436686</v>
       </c>
       <c r="R46" t="n">
-        <v>7036788</v>
+        <v>7036815</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6003,21 +6122,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6026,48 +6135,23 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138529</v>
+        <v>124138519</v>
       </c>
       <c r="B47" t="n">
         <v>91030</v>
@@ -6107,10 +6191,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436661</v>
+        <v>436513</v>
       </c>
       <c r="R47" t="n">
-        <v>7036719</v>
+        <v>7036741</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6169,10 +6253,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124120678</v>
+        <v>124138524</v>
       </c>
       <c r="B48" t="n">
-        <v>79892</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6185,42 +6269,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436489</v>
+        <v>436539</v>
       </c>
       <c r="R48" t="n">
-        <v>7036772</v>
+        <v>7036496</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6247,26 +6326,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6275,51 +6339,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124124670</v>
+        <v>124121529</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6332,37 +6371,56 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436446</v>
+        <v>436390</v>
       </c>
       <c r="R49" t="n">
-        <v>7036676</v>
+        <v>7036767</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6391,7 +6449,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6401,7 +6459,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6416,26 +6479,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6453,10 +6496,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124122388</v>
+        <v>124120889</v>
       </c>
       <c r="B50" t="n">
-        <v>57942</v>
+        <v>57529</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6469,41 +6512,27 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6512,13 +6541,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436519</v>
+        <v>436483</v>
       </c>
       <c r="R50" t="n">
-        <v>7036935</v>
+        <v>7036812</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6547,7 +6576,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6557,7 +6586,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6572,6 +6606,26 @@
       <c r="AH50" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6589,10 +6643,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124119822</v>
+        <v>124138505</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6605,37 +6659,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436287</v>
+        <v>436515</v>
       </c>
       <c r="R51" t="n">
-        <v>7036648</v>
+        <v>7036414</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6667,6 +6721,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6675,51 +6734,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138516</v>
+        <v>124138499</v>
       </c>
       <c r="B52" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6728,25 +6762,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6756,10 +6790,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436629</v>
+        <v>436565</v>
       </c>
       <c r="R52" t="n">
-        <v>7036589</v>
+        <v>7036491</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6792,6 +6826,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6818,10 +6857,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124122092</v>
+        <v>124138535</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6834,53 +6873,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436572</v>
+        <v>436609</v>
       </c>
       <c r="R53" t="n">
-        <v>7036828</v>
+        <v>7036617</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6910,26 +6930,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6938,21 +6943,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138522</v>
+        <v>124122815</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436590</v>
+        <v>436455</v>
       </c>
       <c r="R2" t="n">
-        <v>7036784</v>
+        <v>7036885</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +758,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,26 +781,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138490</v>
+        <v>124119822</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436542</v>
+        <v>436287</v>
       </c>
       <c r="R3" t="n">
-        <v>7036748</v>
+        <v>7036648</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,11 +880,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -868,26 +888,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138511</v>
+        <v>124138522</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,46 +945,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436582</v>
+        <v>436590</v>
       </c>
       <c r="R4" t="n">
-        <v>7036714</v>
+        <v>7036784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138516</v>
+        <v>124138489</v>
       </c>
       <c r="B5" t="n">
-        <v>91457</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1043,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436629</v>
+        <v>436553</v>
       </c>
       <c r="R5" t="n">
-        <v>7036589</v>
+        <v>7036719</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1107,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138527</v>
+        <v>124138517</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1140,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436655</v>
+        <v>436623</v>
       </c>
       <c r="R6" t="n">
-        <v>7036737</v>
+        <v>7036558</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1411,10 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124120703</v>
+        <v>124123983</v>
       </c>
       <c r="B9" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,31 +1461,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1456,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436492</v>
+        <v>436575</v>
       </c>
       <c r="R9" t="n">
-        <v>7036774</v>
+        <v>7036750</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1501,12 +1539,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,22 +1563,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1558,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124121853</v>
+        <v>124138524</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1574,37 +1612,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436611</v>
+        <v>436539</v>
       </c>
       <c r="R10" t="n">
-        <v>7036804</v>
+        <v>7036496</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,26 +1669,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1659,51 +1682,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124120741</v>
+        <v>124138502</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,42 +1714,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436483</v>
+        <v>436558</v>
       </c>
       <c r="R11" t="n">
-        <v>7036788</v>
+        <v>7036469</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,19 +1779,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:26</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,51 +1797,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124120678</v>
+        <v>124138511</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,42 +1829,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436489</v>
+        <v>436582</v>
       </c>
       <c r="R12" t="n">
-        <v>7036772</v>
+        <v>7036714</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,26 +1898,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1948,51 +1911,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124122460</v>
+        <v>124122388</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2005,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2027,9 +1965,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2043,13 +1986,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436516</v>
+        <v>436519</v>
       </c>
       <c r="R13" t="n">
-        <v>7036958</v>
+        <v>7036935</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2078,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2088,12 +2031,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2125,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138508</v>
+        <v>124122426</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2137,53 +2075,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436630</v>
+        <v>436497</v>
       </c>
       <c r="R14" t="n">
-        <v>7036552</v>
+        <v>7036929</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2210,11 +2136,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2223,26 +2159,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138517</v>
+        <v>124138521</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,21 +2216,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2279,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436623</v>
+        <v>436548</v>
       </c>
       <c r="R15" t="n">
-        <v>7036558</v>
+        <v>7036699</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2341,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124122815</v>
+        <v>124138525</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2357,47 +2318,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436455</v>
+        <v>436632</v>
       </c>
       <c r="R16" t="n">
-        <v>7036885</v>
+        <v>7036740</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2424,21 +2375,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2447,31 +2388,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138484</v>
+        <v>124138494</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2484,21 +2420,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2508,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436524</v>
+        <v>436665</v>
       </c>
       <c r="R17" t="n">
-        <v>7036571</v>
+        <v>7036654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2544,6 +2480,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2570,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138525</v>
+        <v>124120467</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2582,41 +2523,60 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436632</v>
+        <v>436380</v>
       </c>
       <c r="R18" t="n">
-        <v>7036740</v>
+        <v>7036719</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2643,11 +2603,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2656,26 +2626,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138494</v>
+        <v>124120703</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,41 +2659,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436665</v>
+        <v>436492</v>
       </c>
       <c r="R19" t="n">
-        <v>7036654</v>
+        <v>7036774</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2745,14 +2725,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,26 +2753,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138492</v>
+        <v>124124067</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,34 +2810,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436577</v>
+        <v>436566</v>
       </c>
       <c r="R20" t="n">
-        <v>7036686</v>
+        <v>7036754</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,14 +2872,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,26 +2895,51 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124124670</v>
+        <v>124138514</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,37 +2952,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436446</v>
+        <v>436467</v>
       </c>
       <c r="R21" t="n">
-        <v>7036676</v>
+        <v>7036669</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2959,19 +3009,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,51 +3027,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138518</v>
+        <v>124122092</v>
       </c>
       <c r="B22" t="n">
-        <v>57883</v>
+        <v>57666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,42 +3055,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436552</v>
+        <v>436572</v>
       </c>
       <c r="R22" t="n">
-        <v>7036703</v>
+        <v>7036828</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3100,11 +3135,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3113,26 +3163,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138489</v>
+        <v>124138487</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3200,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3224,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436553</v>
+        <v>436511</v>
       </c>
       <c r="R23" t="n">
-        <v>7036719</v>
+        <v>7036406</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,11 +3260,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,10 +3286,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124121014</v>
+        <v>124138490</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,37 +3302,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436440</v>
+        <v>436542</v>
       </c>
       <c r="R24" t="n">
-        <v>7036807</v>
+        <v>7036748</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3309,19 +3359,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3332,51 +3377,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124122264</v>
+        <v>124138499</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3385,20 +3405,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3406,39 +3426,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436515</v>
+        <v>436565</v>
       </c>
       <c r="R25" t="n">
-        <v>7036863</v>
+        <v>7036491</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3470,6 +3471,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3478,31 +3484,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124121762</v>
+        <v>124121529</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3515,34 +3516,53 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436547</v>
+        <v>436390</v>
       </c>
       <c r="R26" t="n">
-        <v>7036757</v>
+        <v>7036767</v>
       </c>
       <c r="S26" t="n">
         <v>11</v>
@@ -3574,7 +3594,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3584,7 +3604,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,26 +3624,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3636,10 +3641,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124124067</v>
+        <v>124138534</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,39 +3657,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436566</v>
+        <v>436665</v>
       </c>
       <c r="R27" t="n">
-        <v>7036754</v>
+        <v>7036708</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,21 +3714,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3737,51 +3727,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138487</v>
+        <v>124124670</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3794,37 +3759,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436511</v>
+        <v>436446</v>
       </c>
       <c r="R28" t="n">
-        <v>7036406</v>
+        <v>7036676</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3851,11 +3816,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3864,26 +3839,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124122426</v>
+        <v>124123667</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3896,37 +3896,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436497</v>
+        <v>436566</v>
       </c>
       <c r="R29" t="n">
-        <v>7036929</v>
+        <v>7036880</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3955,7 +3960,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3965,7 +3970,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3994,12 +4004,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4017,10 +4027,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124123983</v>
+        <v>124121014</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4033,42 +4043,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436575</v>
+        <v>436440</v>
       </c>
       <c r="R30" t="n">
-        <v>7036750</v>
+        <v>7036807</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4097,7 +4102,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4107,12 +4112,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124120544</v>
+        <v>124138484</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4180,37 +4180,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436449</v>
+        <v>436524</v>
       </c>
       <c r="R31" t="n">
-        <v>7036726</v>
+        <v>7036571</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4237,21 +4237,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4260,51 +4250,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138531</v>
+        <v>124138486</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4317,21 +4282,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4341,10 +4306,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436554</v>
+        <v>436686</v>
       </c>
       <c r="R32" t="n">
-        <v>7036548</v>
+        <v>7036815</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4377,11 +4342,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4408,10 +4368,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124119822</v>
+        <v>124120889</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4424,37 +4384,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436287</v>
+        <v>436483</v>
       </c>
       <c r="R33" t="n">
-        <v>7036648</v>
+        <v>7036812</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4481,11 +4446,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4512,12 +4492,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4535,10 +4515,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124124271</v>
+        <v>124138527</v>
       </c>
       <c r="B34" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4547,43 +4527,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436563</v>
+        <v>436655</v>
       </c>
       <c r="R34" t="n">
-        <v>7036748</v>
+        <v>7036737</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4613,21 +4588,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4636,51 +4601,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138521</v>
+        <v>124121853</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4693,37 +4633,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436548</v>
+        <v>436611</v>
       </c>
       <c r="R35" t="n">
-        <v>7036699</v>
+        <v>7036804</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4750,11 +4690,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4763,26 +4718,51 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138514</v>
+        <v>124138535</v>
       </c>
       <c r="B36" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4795,21 +4775,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4819,10 +4799,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436467</v>
+        <v>436609</v>
       </c>
       <c r="R36" t="n">
-        <v>7036669</v>
+        <v>7036617</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4855,11 +4835,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4886,10 +4861,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124121048</v>
+        <v>124124271</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4898,25 +4873,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4931,13 +4906,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436428</v>
+        <v>436563</v>
       </c>
       <c r="R37" t="n">
-        <v>7036785</v>
+        <v>7036748</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4966,7 +4941,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4976,7 +4951,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5028,10 +5003,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138497</v>
+        <v>124120544</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5044,37 +5019,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436619</v>
+        <v>436449</v>
       </c>
       <c r="R38" t="n">
-        <v>7036576</v>
+        <v>7036726</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5101,14 +5076,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5119,23 +5099,48 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138534</v>
+        <v>124121762</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -5171,17 +5176,17 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436665</v>
+        <v>436547</v>
       </c>
       <c r="R39" t="n">
-        <v>7036708</v>
+        <v>7036757</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5208,11 +5213,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5221,26 +5236,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122388</v>
+        <v>124122460</v>
       </c>
       <c r="B40" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5253,21 +5293,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5275,14 +5315,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5296,13 +5331,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436519</v>
+        <v>436516</v>
       </c>
       <c r="R40" t="n">
-        <v>7036935</v>
+        <v>7036958</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5331,7 +5366,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5341,7 +5376,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5373,10 +5413,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124123667</v>
+        <v>124138531</v>
       </c>
       <c r="B41" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5389,42 +5429,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436566</v>
+        <v>436554</v>
       </c>
       <c r="R41" t="n">
-        <v>7036880</v>
+        <v>7036548</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5451,24 +5486,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5479,51 +5504,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124123595</v>
+        <v>124120678</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5536,37 +5536,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436560</v>
+        <v>436489</v>
       </c>
       <c r="R42" t="n">
-        <v>7036869</v>
+        <v>7036772</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5595,7 +5600,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5605,7 +5610,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5624,22 +5634,22 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5657,10 +5667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124122092</v>
+        <v>124138497</v>
       </c>
       <c r="B43" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5673,53 +5683,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436572</v>
+        <v>436619</v>
       </c>
       <c r="R43" t="n">
-        <v>7036828</v>
+        <v>7036576</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5749,24 +5740,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5777,31 +5758,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124120467</v>
+        <v>124138508</v>
       </c>
       <c r="B44" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5814,21 +5790,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5836,16 +5812,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5853,17 +5822,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436380</v>
+        <v>436630</v>
       </c>
       <c r="R44" t="n">
-        <v>7036719</v>
+        <v>7036552</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5890,21 +5859,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5913,31 +5872,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138502</v>
+        <v>124138516</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>91457</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5946,46 +5900,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436558</v>
+        <v>436629</v>
       </c>
       <c r="R45" t="n">
-        <v>7036469</v>
+        <v>7036589</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6018,11 +5964,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6049,10 +5990,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138486</v>
+        <v>124122264</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>57883</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6061,41 +6002,60 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436686</v>
+        <v>436515</v>
       </c>
       <c r="R46" t="n">
-        <v>7036815</v>
+        <v>7036863</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6135,26 +6095,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138519</v>
+        <v>124138518</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6163,38 +6128,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436513</v>
+        <v>436552</v>
       </c>
       <c r="R47" t="n">
-        <v>7036741</v>
+        <v>7036703</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6253,10 +6222,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138524</v>
+        <v>124138505</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6269,21 +6238,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6293,10 +6262,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436539</v>
+        <v>436515</v>
       </c>
       <c r="R48" t="n">
-        <v>7036496</v>
+        <v>7036414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6329,6 +6298,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6355,10 +6329,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124121529</v>
+        <v>124121048</v>
       </c>
       <c r="B49" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6371,41 +6345,27 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6414,13 +6374,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436390</v>
+        <v>436428</v>
       </c>
       <c r="R49" t="n">
-        <v>7036767</v>
+        <v>7036785</v>
       </c>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6449,7 +6409,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6459,12 +6419,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6479,6 +6434,26 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6496,10 +6471,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124120889</v>
+        <v>124123595</v>
       </c>
       <c r="B50" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6512,42 +6487,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436483</v>
+        <v>436560</v>
       </c>
       <c r="R50" t="n">
-        <v>7036812</v>
+        <v>7036869</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6576,7 +6546,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6586,12 +6556,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6620,12 +6585,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6643,7 +6608,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138505</v>
+        <v>124138492</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6683,10 +6648,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436515</v>
+        <v>436577</v>
       </c>
       <c r="R51" t="n">
-        <v>7036414</v>
+        <v>7036686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6723,7 +6688,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6750,10 +6715,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138499</v>
+        <v>124120741</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6766,37 +6731,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436565</v>
+        <v>436483</v>
       </c>
       <c r="R52" t="n">
-        <v>7036491</v>
+        <v>7036788</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6823,14 +6793,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6841,26 +6816,51 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138535</v>
+        <v>124138519</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6873,21 +6873,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436609</v>
+        <v>436513</v>
       </c>
       <c r="R53" t="n">
-        <v>7036617</v>
+        <v>7036741</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124122815</v>
+        <v>124138522</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,47 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436455</v>
+        <v>436590</v>
       </c>
       <c r="R2" t="n">
-        <v>7036885</v>
+        <v>7036784</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,21 +748,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,31 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124119822</v>
+        <v>124138489</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436287</v>
+        <v>436553</v>
       </c>
       <c r="R3" t="n">
-        <v>7036648</v>
+        <v>7036719</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,6 +855,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,51 +868,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138522</v>
+        <v>124119822</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436590</v>
+        <v>436287</v>
       </c>
       <c r="R4" t="n">
-        <v>7036784</v>
+        <v>7036648</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,26 +970,51 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138489</v>
+        <v>124122815</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,19 +1045,29 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436553</v>
+        <v>436455</v>
       </c>
       <c r="R5" t="n">
-        <v>7036719</v>
+        <v>7036885</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,14 +1094,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,16 +1117,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138490</v>
+        <v>124121529</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3302,37 +3302,56 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436542</v>
+        <v>436390</v>
       </c>
       <c r="R24" t="n">
-        <v>7036748</v>
+        <v>7036767</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3359,14 +3378,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3377,26 +3406,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138499</v>
+        <v>124138534</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,21 +3443,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3433,10 +3467,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436565</v>
+        <v>436665</v>
       </c>
       <c r="R25" t="n">
-        <v>7036491</v>
+        <v>7036708</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3469,11 +3503,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3500,10 +3529,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124121529</v>
+        <v>124124670</v>
       </c>
       <c r="B26" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3516,56 +3545,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436390</v>
+        <v>436446</v>
       </c>
       <c r="R26" t="n">
-        <v>7036767</v>
+        <v>7036676</v>
       </c>
       <c r="S26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3594,7 +3604,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3604,12 +3614,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3624,6 +3629,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3641,10 +3666,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138534</v>
+        <v>124123667</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3657,37 +3682,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436665</v>
+        <v>436566</v>
       </c>
       <c r="R27" t="n">
-        <v>7036708</v>
+        <v>7036880</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3714,11 +3744,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3727,26 +3772,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124124670</v>
+        <v>124138490</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3759,37 +3829,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436446</v>
+        <v>436542</v>
       </c>
       <c r="R28" t="n">
-        <v>7036676</v>
+        <v>7036748</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3816,19 +3886,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:19</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3839,51 +3904,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124123667</v>
+        <v>124138499</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3896,16 +3936,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3914,24 +3954,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436566</v>
+        <v>436565</v>
       </c>
       <c r="R29" t="n">
-        <v>7036880</v>
+        <v>7036491</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3958,24 +3993,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3986,41 +4011,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4368,10 +4368,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124120889</v>
+        <v>124138527</v>
       </c>
       <c r="B33" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4384,39 +4384,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436483</v>
+        <v>436655</v>
       </c>
       <c r="R33" t="n">
-        <v>7036812</v>
+        <v>7036737</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4446,26 +4441,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4474,51 +4454,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138527</v>
+        <v>124120889</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4531,34 +4486,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436655</v>
+        <v>436483</v>
       </c>
       <c r="R34" t="n">
-        <v>7036737</v>
+        <v>7036812</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4588,11 +4548,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4601,16 +4576,41 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -6116,10 +6116,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138518</v>
+        <v>124121048</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6128,45 +6128,46 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436552</v>
+        <v>436428</v>
       </c>
       <c r="R47" t="n">
-        <v>7036703</v>
+        <v>7036785</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6193,11 +6194,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6206,26 +6217,51 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138505</v>
+        <v>124123595</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6238,37 +6274,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436515</v>
+        <v>436560</v>
       </c>
       <c r="R48" t="n">
-        <v>7036414</v>
+        <v>7036869</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6295,14 +6331,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6313,26 +6354,51 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124121048</v>
+        <v>124138505</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6345,42 +6411,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436428</v>
+        <v>436515</v>
       </c>
       <c r="R49" t="n">
-        <v>7036785</v>
+        <v>7036414</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6407,19 +6468,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6430,51 +6486,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124123595</v>
+        <v>124138518</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6483,41 +6514,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436560</v>
+        <v>436552</v>
       </c>
       <c r="R50" t="n">
-        <v>7036869</v>
+        <v>7036703</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6544,21 +6579,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6567,51 +6592,26 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138492</v>
+        <v>124120741</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6624,37 +6624,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436577</v>
+        <v>436483</v>
       </c>
       <c r="R51" t="n">
-        <v>7036686</v>
+        <v>7036788</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6681,14 +6686,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6699,26 +6709,51 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124120741</v>
+        <v>124138492</v>
       </c>
       <c r="B52" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6731,42 +6766,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436483</v>
+        <v>436577</v>
       </c>
       <c r="R52" t="n">
-        <v>7036788</v>
+        <v>7036686</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6793,19 +6823,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>09:26</t>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6816,41 +6841,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138522</v>
+        <v>124138502</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436590</v>
+        <v>436558</v>
       </c>
       <c r="R2" t="n">
-        <v>7036784</v>
+        <v>7036469</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138489</v>
+        <v>124124670</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +806,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436553</v>
+        <v>436446</v>
       </c>
       <c r="R3" t="n">
-        <v>7036719</v>
+        <v>7036676</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,14 +863,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -868,26 +886,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124119822</v>
+        <v>124138525</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +943,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436287</v>
+        <v>436632</v>
       </c>
       <c r="R4" t="n">
-        <v>7036648</v>
+        <v>7036740</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,51 +1013,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124122815</v>
+        <v>124138484</v>
       </c>
       <c r="B5" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,47 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436455</v>
+        <v>436524</v>
       </c>
       <c r="R5" t="n">
-        <v>7036885</v>
+        <v>7036571</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,21 +1102,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1117,31 +1115,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138517</v>
+        <v>124138508</v>
       </c>
       <c r="B6" t="n">
-        <v>91299</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1143,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436623</v>
+        <v>436630</v>
       </c>
       <c r="R6" t="n">
-        <v>7036558</v>
+        <v>7036552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138529</v>
+        <v>124138505</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436661</v>
+        <v>436515</v>
       </c>
       <c r="R7" t="n">
-        <v>7036719</v>
+        <v>7036414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,6 +1321,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138500</v>
+        <v>124138514</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1382,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436566</v>
+        <v>436467</v>
       </c>
       <c r="R8" t="n">
-        <v>7036478</v>
+        <v>7036669</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1432,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1449,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123983</v>
+        <v>124138529</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,39 +1475,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436575</v>
+        <v>436661</v>
       </c>
       <c r="R9" t="n">
-        <v>7036750</v>
+        <v>7036719</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,26 +1532,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1555,48 +1545,23 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138524</v>
+        <v>124138521</v>
       </c>
       <c r="B10" t="n">
         <v>91030</v>
@@ -1636,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436539</v>
+        <v>436548</v>
       </c>
       <c r="R10" t="n">
-        <v>7036496</v>
+        <v>7036699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138502</v>
+        <v>124138517</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,42 +1679,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436558</v>
+        <v>436623</v>
       </c>
       <c r="R11" t="n">
-        <v>7036469</v>
+        <v>7036558</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,11 +1739,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138511</v>
+        <v>124138492</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,46 +1781,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436582</v>
+        <v>436577</v>
       </c>
       <c r="R12" t="n">
-        <v>7036714</v>
+        <v>7036686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2063,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122426</v>
+        <v>124122460</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,37 +2024,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436497</v>
+        <v>436516</v>
       </c>
       <c r="R14" t="n">
-        <v>7036929</v>
+        <v>7036958</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,7 +2107,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,26 +2127,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2200,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138521</v>
+        <v>124120889</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,34 +2160,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436548</v>
+        <v>436483</v>
       </c>
       <c r="R15" t="n">
-        <v>7036699</v>
+        <v>7036812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2273,11 +2222,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2286,26 +2250,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138525</v>
+        <v>124138500</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2318,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436632</v>
+        <v>436566</v>
       </c>
       <c r="R16" t="n">
-        <v>7036740</v>
+        <v>7036478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,6 +2367,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,10 +2398,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138494</v>
+        <v>124121048</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2420,37 +2414,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436665</v>
+        <v>436428</v>
       </c>
       <c r="R17" t="n">
-        <v>7036654</v>
+        <v>7036785</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,14 +2476,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2495,26 +2499,51 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124120467</v>
+        <v>124138522</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,60 +2552,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436380</v>
+        <v>436590</v>
       </c>
       <c r="R18" t="n">
-        <v>7036719</v>
+        <v>7036784</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,21 +2613,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2626,31 +2626,26 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124120703</v>
+        <v>124138486</v>
       </c>
       <c r="B19" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,46 +2654,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436492</v>
+        <v>436686</v>
       </c>
       <c r="R19" t="n">
-        <v>7036774</v>
+        <v>7036815</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,26 +2715,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2753,51 +2728,26 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124124067</v>
+        <v>124138487</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,39 +2760,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436566</v>
+        <v>436511</v>
       </c>
       <c r="R20" t="n">
-        <v>7036754</v>
+        <v>7036406</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2872,21 +2817,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2895,51 +2830,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138514</v>
+        <v>124138494</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2952,16 +2862,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2976,10 +2886,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436467</v>
+        <v>436665</v>
       </c>
       <c r="R21" t="n">
-        <v>7036669</v>
+        <v>7036654</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3016,7 +2926,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124122092</v>
+        <v>124138497</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3059,53 +2969,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436572</v>
+        <v>436619</v>
       </c>
       <c r="R22" t="n">
-        <v>7036828</v>
+        <v>7036576</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3135,24 +3026,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3163,31 +3044,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138487</v>
+        <v>124121762</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3200,37 +3076,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436511</v>
+        <v>436547</v>
       </c>
       <c r="R23" t="n">
-        <v>7036406</v>
+        <v>7036757</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3257,11 +3133,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3270,26 +3156,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124121529</v>
+        <v>124121014</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3302,56 +3213,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436390</v>
+        <v>436440</v>
       </c>
       <c r="R24" t="n">
-        <v>7036767</v>
+        <v>7036807</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3380,7 +3272,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3390,12 +3282,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,6 +3297,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3427,7 +3334,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138534</v>
+        <v>124121853</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3463,17 +3370,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436665</v>
+        <v>436611</v>
       </c>
       <c r="R25" t="n">
-        <v>7036708</v>
+        <v>7036804</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3500,11 +3407,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3513,23 +3435,48 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124124670</v>
+        <v>124138534</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3565,17 +3512,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436446</v>
+        <v>436665</v>
       </c>
       <c r="R26" t="n">
-        <v>7036676</v>
+        <v>7036708</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3602,21 +3549,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3625,51 +3562,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124123667</v>
+        <v>124138518</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3678,20 +3590,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3700,24 +3612,23 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436566</v>
+        <v>436552</v>
       </c>
       <c r="R27" t="n">
-        <v>7036880</v>
+        <v>7036703</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3744,26 +3655,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3772,51 +3668,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138490</v>
+        <v>124120678</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3829,37 +3700,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436542</v>
+        <v>436489</v>
       </c>
       <c r="R28" t="n">
-        <v>7036748</v>
+        <v>7036772</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3886,14 +3762,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3904,23 +3790,48 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138499</v>
+        <v>124138490</v>
       </c>
       <c r="B29" t="n">
         <v>57513</v>
@@ -3960,10 +3871,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436565</v>
+        <v>436542</v>
       </c>
       <c r="R29" t="n">
-        <v>7036491</v>
+        <v>7036748</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4027,10 +3938,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124121014</v>
+        <v>124122264</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4039,41 +3950,60 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436440</v>
+        <v>436515</v>
       </c>
       <c r="R30" t="n">
-        <v>7036807</v>
+        <v>7036863</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4100,21 +4030,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4127,26 +4047,6 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4164,10 +4064,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138484</v>
+        <v>124121529</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4180,37 +4080,56 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436524</v>
+        <v>436390</v>
       </c>
       <c r="R31" t="n">
-        <v>7036571</v>
+        <v>7036767</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4237,11 +4156,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4250,26 +4184,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138486</v>
+        <v>124124067</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4282,34 +4221,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436686</v>
+        <v>436566</v>
       </c>
       <c r="R32" t="n">
-        <v>7036815</v>
+        <v>7036754</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4339,11 +4283,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4352,23 +4306,48 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138527</v>
+        <v>124138519</v>
       </c>
       <c r="B33" t="n">
         <v>91030</v>
@@ -4408,10 +4387,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436655</v>
+        <v>436513</v>
       </c>
       <c r="R33" t="n">
-        <v>7036737</v>
+        <v>7036741</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4470,10 +4449,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124120889</v>
+        <v>124120467</v>
       </c>
       <c r="B34" t="n">
-        <v>57529</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4482,20 +4461,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4503,10 +4482,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4515,13 +4508,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436483</v>
+        <v>436380</v>
       </c>
       <c r="R34" t="n">
-        <v>7036812</v>
+        <v>7036719</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4550,7 +4543,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4560,12 +4553,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4580,26 +4568,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4617,10 +4585,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124121853</v>
+        <v>124138524</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4633,37 +4601,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436611</v>
+        <v>436539</v>
       </c>
       <c r="R35" t="n">
-        <v>7036804</v>
+        <v>7036496</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4690,26 +4658,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4718,48 +4671,23 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138535</v>
+        <v>124138531</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4799,10 +4727,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436609</v>
+        <v>436554</v>
       </c>
       <c r="R36" t="n">
-        <v>7036617</v>
+        <v>7036548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4835,6 +4763,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4861,10 +4794,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124124271</v>
+        <v>124123595</v>
       </c>
       <c r="B37" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4873,46 +4806,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436563</v>
+        <v>436560</v>
       </c>
       <c r="R37" t="n">
-        <v>7036748</v>
+        <v>7036869</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4941,7 +4869,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4951,7 +4879,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4980,12 +4908,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5003,10 +4931,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124120544</v>
+        <v>124138516</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5015,41 +4943,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436449</v>
+        <v>436629</v>
       </c>
       <c r="R38" t="n">
-        <v>7036726</v>
+        <v>7036589</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5076,21 +5004,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5099,51 +5017,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124121762</v>
+        <v>124138489</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5156,37 +5049,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436547</v>
+        <v>436553</v>
       </c>
       <c r="R39" t="n">
-        <v>7036757</v>
+        <v>7036719</v>
       </c>
       <c r="S39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5213,19 +5106,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5236,51 +5124,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122460</v>
+        <v>124120741</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5293,36 +5156,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5331,13 +5185,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436516</v>
+        <v>436483</v>
       </c>
       <c r="R40" t="n">
-        <v>7036958</v>
+        <v>7036788</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5366,7 +5220,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5376,12 +5230,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5396,6 +5245,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5413,10 +5282,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138531</v>
+        <v>124120703</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5425,41 +5294,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436554</v>
+        <v>436492</v>
       </c>
       <c r="R41" t="n">
-        <v>7036548</v>
+        <v>7036774</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5486,14 +5360,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5504,26 +5388,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124120678</v>
+        <v>124138535</v>
       </c>
       <c r="B42" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5536,42 +5445,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436489</v>
+        <v>436609</v>
       </c>
       <c r="R42" t="n">
-        <v>7036772</v>
+        <v>7036617</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5598,26 +5502,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5626,48 +5515,23 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138497</v>
+        <v>124123983</v>
       </c>
       <c r="B43" t="n">
         <v>57513</v>
@@ -5701,16 +5565,21 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436619</v>
+        <v>436575</v>
       </c>
       <c r="R43" t="n">
-        <v>7036576</v>
+        <v>7036750</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5740,14 +5609,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5758,26 +5637,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138508</v>
+        <v>124138499</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5786,50 +5690,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436630</v>
+        <v>436565</v>
       </c>
       <c r="R44" t="n">
-        <v>7036552</v>
+        <v>7036491</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5862,6 +5754,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5888,10 +5785,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138516</v>
+        <v>124138511</v>
       </c>
       <c r="B45" t="n">
-        <v>91457</v>
+        <v>57666</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5900,38 +5797,50 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436629</v>
+        <v>436582</v>
       </c>
       <c r="R45" t="n">
-        <v>7036589</v>
+        <v>7036714</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5990,10 +5899,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124122264</v>
+        <v>124122426</v>
       </c>
       <c r="B46" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6002,57 +5911,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436515</v>
+        <v>436497</v>
       </c>
       <c r="R46" t="n">
-        <v>7036863</v>
+        <v>7036929</v>
       </c>
       <c r="S46" t="n">
         <v>9</v>
@@ -6082,11 +5972,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6099,6 +5999,26 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6116,10 +6036,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124121048</v>
+        <v>124119822</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6132,39 +6052,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436428</v>
+        <v>436287</v>
       </c>
       <c r="R47" t="n">
-        <v>7036785</v>
+        <v>7036648</v>
       </c>
       <c r="S47" t="n">
         <v>8</v>
@@ -6194,21 +6109,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6235,12 +6140,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6258,10 +6163,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124123595</v>
+        <v>124138527</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6274,37 +6179,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436560</v>
+        <v>436655</v>
       </c>
       <c r="R48" t="n">
-        <v>7036869</v>
+        <v>7036737</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6331,21 +6236,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6354,51 +6249,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138505</v>
+        <v>124124271</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>91700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6407,38 +6277,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436515</v>
+        <v>436563</v>
       </c>
       <c r="R49" t="n">
-        <v>7036414</v>
+        <v>7036748</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6468,14 +6343,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6486,26 +6366,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138518</v>
+        <v>124120544</v>
       </c>
       <c r="B50" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6514,45 +6419,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436552</v>
+        <v>436449</v>
       </c>
       <c r="R50" t="n">
-        <v>7036703</v>
+        <v>7036726</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6579,11 +6480,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6592,26 +6503,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124120741</v>
+        <v>124123667</v>
       </c>
       <c r="B51" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6624,27 +6560,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6653,13 +6589,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436483</v>
+        <v>436566</v>
       </c>
       <c r="R51" t="n">
-        <v>7036788</v>
+        <v>7036880</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6688,7 +6624,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6698,7 +6634,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6727,12 +6668,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6750,10 +6691,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138492</v>
+        <v>124122815</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6766,16 +6707,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6784,19 +6725,29 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436577</v>
+        <v>436455</v>
       </c>
       <c r="R52" t="n">
-        <v>7036686</v>
+        <v>7036885</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6823,14 +6774,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6841,26 +6797,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138519</v>
+        <v>124122092</v>
       </c>
       <c r="B53" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6873,34 +6834,53 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436513</v>
+        <v>436572</v>
       </c>
       <c r="R53" t="n">
-        <v>7036741</v>
+        <v>7036828</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6930,11 +6910,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6943,16 +6938,21 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124122388</v>
+        <v>124122460</v>
       </c>
       <c r="B13" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1910,14 +1910,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1931,13 +1926,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436519</v>
+        <v>436516</v>
       </c>
       <c r="R13" t="n">
-        <v>7036935</v>
+        <v>7036958</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1966,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1976,7 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122460</v>
+        <v>124122388</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2046,9 +2046,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2062,13 +2067,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436516</v>
+        <v>436519</v>
       </c>
       <c r="R14" t="n">
-        <v>7036958</v>
+        <v>7036935</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,12 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138500</v>
+        <v>124121048</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,37 +2307,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436566</v>
+        <v>436428</v>
       </c>
       <c r="R16" t="n">
-        <v>7036478</v>
+        <v>7036785</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,14 +2369,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2382,26 +2392,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124121048</v>
+        <v>124138500</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2414,42 +2449,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436428</v>
+        <v>436566</v>
       </c>
       <c r="R17" t="n">
-        <v>7036785</v>
+        <v>7036478</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2476,19 +2506,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,51 +2524,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138522</v>
+        <v>124138486</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436590</v>
+        <v>436686</v>
       </c>
       <c r="R18" t="n">
-        <v>7036784</v>
+        <v>7036815</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138486</v>
+        <v>124138522</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436686</v>
+        <v>436590</v>
       </c>
       <c r="R19" t="n">
-        <v>7036815</v>
+        <v>7036784</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124121014</v>
+        <v>124138518</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57883</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,41 +3209,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436440</v>
+        <v>436552</v>
       </c>
       <c r="R24" t="n">
-        <v>7036807</v>
+        <v>7036703</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3270,21 +3274,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3293,51 +3287,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124121853</v>
+        <v>124120678</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3350,37 +3319,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436611</v>
+        <v>436489</v>
       </c>
       <c r="R25" t="n">
-        <v>7036804</v>
+        <v>7036772</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3409,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3419,12 +3393,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,22 +3417,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3476,7 +3450,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138534</v>
+        <v>124121014</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3512,17 +3486,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436665</v>
+        <v>436440</v>
       </c>
       <c r="R26" t="n">
-        <v>7036708</v>
+        <v>7036807</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3549,11 +3523,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3562,26 +3546,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138518</v>
+        <v>124121853</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,45 +3599,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436552</v>
+        <v>436611</v>
       </c>
       <c r="R27" t="n">
-        <v>7036703</v>
+        <v>7036804</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3655,11 +3660,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3668,26 +3688,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124120678</v>
+        <v>124138534</v>
       </c>
       <c r="B28" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3700,42 +3745,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436489</v>
+        <v>436665</v>
       </c>
       <c r="R28" t="n">
-        <v>7036772</v>
+        <v>7036708</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3762,26 +3802,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3790,51 +3815,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138490</v>
+        <v>124122264</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3843,20 +3843,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3864,20 +3864,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436542</v>
+        <v>436515</v>
       </c>
       <c r="R29" t="n">
-        <v>7036748</v>
+        <v>7036863</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3909,11 +3928,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3922,26 +3936,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124122264</v>
+        <v>124138490</v>
       </c>
       <c r="B30" t="n">
-        <v>57883</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3950,20 +3969,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3971,39 +3990,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436515</v>
+        <v>436542</v>
       </c>
       <c r="R30" t="n">
-        <v>7036863</v>
+        <v>7036748</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4035,6 +4035,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4043,21 +4048,16 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4205,10 +4205,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124124067</v>
+        <v>124138519</v>
       </c>
       <c r="B32" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4221,39 +4221,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436566</v>
+        <v>436513</v>
       </c>
       <c r="R32" t="n">
-        <v>7036754</v>
+        <v>7036741</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4283,21 +4278,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4306,51 +4291,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124138519</v>
+        <v>124124067</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>91008</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4363,34 +4323,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436513</v>
+        <v>436566</v>
       </c>
       <c r="R33" t="n">
-        <v>7036741</v>
+        <v>7036754</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4420,11 +4385,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4433,16 +4408,41 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138525</v>
+        <v>124138484</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436632</v>
+        <v>436524</v>
       </c>
       <c r="R4" t="n">
-        <v>7036740</v>
+        <v>7036571</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138484</v>
+        <v>124138525</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436524</v>
+        <v>436632</v>
       </c>
       <c r="R5" t="n">
-        <v>7036571</v>
+        <v>7036740</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124122460</v>
+        <v>124122388</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57942</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1910,9 +1910,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1926,13 +1931,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436516</v>
+        <v>436519</v>
       </c>
       <c r="R13" t="n">
-        <v>7036958</v>
+        <v>7036935</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,7 +1966,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1971,12 +1976,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,10 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122388</v>
+        <v>124122460</v>
       </c>
       <c r="B14" t="n">
-        <v>57942</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,21 +2024,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2046,14 +2046,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2067,13 +2062,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436519</v>
+        <v>436516</v>
       </c>
       <c r="R14" t="n">
-        <v>7036935</v>
+        <v>7036958</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2107,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2540,10 +2540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138486</v>
+        <v>124138522</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436686</v>
+        <v>436590</v>
       </c>
       <c r="R18" t="n">
-        <v>7036815</v>
+        <v>7036784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138522</v>
+        <v>124138486</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,21 +2658,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436590</v>
+        <v>436686</v>
       </c>
       <c r="R19" t="n">
-        <v>7036784</v>
+        <v>7036815</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6163,10 +6163,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138527</v>
+        <v>124122815</v>
       </c>
       <c r="B48" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6179,37 +6179,47 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436655</v>
+        <v>436455</v>
       </c>
       <c r="R48" t="n">
-        <v>7036737</v>
+        <v>7036885</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6236,11 +6246,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6249,26 +6269,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124124271</v>
+        <v>124138527</v>
       </c>
       <c r="B49" t="n">
-        <v>91700</v>
+        <v>91030</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6277,43 +6302,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436563</v>
+        <v>436655</v>
       </c>
       <c r="R49" t="n">
-        <v>7036748</v>
+        <v>7036737</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6343,21 +6363,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6366,51 +6376,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124120544</v>
+        <v>124124271</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6419,41 +6404,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436449</v>
+        <v>436563</v>
       </c>
       <c r="R50" t="n">
-        <v>7036726</v>
+        <v>7036748</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6482,7 +6472,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6492,7 +6482,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6521,12 +6511,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6544,10 +6534,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124123667</v>
+        <v>124120544</v>
       </c>
       <c r="B51" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6560,39 +6550,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436566</v>
+        <v>436449</v>
       </c>
       <c r="R51" t="n">
-        <v>7036880</v>
+        <v>7036726</v>
       </c>
       <c r="S51" t="n">
         <v>7</v>
@@ -6624,7 +6609,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6634,12 +6619,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6668,12 +6648,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6691,10 +6671,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124122815</v>
+        <v>124123667</v>
       </c>
       <c r="B52" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6707,16 +6687,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6727,12 +6707,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6741,13 +6716,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436455</v>
+        <v>436566</v>
       </c>
       <c r="R52" t="n">
-        <v>7036885</v>
+        <v>7036880</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6776,7 +6751,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6786,7 +6761,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6801,6 +6781,26 @@
       <c r="AH52" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124138502</v>
+        <v>124122092</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -691,42 +691,53 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436558</v>
+        <v>436572</v>
       </c>
       <c r="R2" t="n">
-        <v>7036469</v>
+        <v>7036828</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,14 +767,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,26 +795,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124124670</v>
+        <v>124138525</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,37 +832,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436446</v>
+        <v>436632</v>
       </c>
       <c r="R3" t="n">
-        <v>7036676</v>
+        <v>7036740</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,21 +889,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -886,51 +902,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138484</v>
+        <v>124138517</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436524</v>
+        <v>436623</v>
       </c>
       <c r="R4" t="n">
-        <v>7036571</v>
+        <v>7036558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138525</v>
+        <v>124138518</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,38 +1032,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436632</v>
+        <v>436552</v>
       </c>
       <c r="R5" t="n">
-        <v>7036740</v>
+        <v>7036703</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138508</v>
+        <v>124119822</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,53 +1138,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436630</v>
+        <v>436287</v>
       </c>
       <c r="R6" t="n">
-        <v>7036552</v>
+        <v>7036648</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,30 +1212,55 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138505</v>
+        <v>124138534</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1261,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436515</v>
+        <v>436665</v>
       </c>
       <c r="R7" t="n">
-        <v>7036414</v>
+        <v>7036708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,11 +1329,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138514</v>
+        <v>124138522</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436467</v>
+        <v>436590</v>
       </c>
       <c r="R8" t="n">
-        <v>7036669</v>
+        <v>7036784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,11 +1431,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124138529</v>
+        <v>124124271</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>91700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,38 +1469,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436661</v>
+        <v>436563</v>
       </c>
       <c r="R9" t="n">
-        <v>7036719</v>
+        <v>7036748</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,11 +1535,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1545,26 +1558,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124138521</v>
+        <v>124120889</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,34 +1615,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436548</v>
+        <v>436483</v>
       </c>
       <c r="R10" t="n">
-        <v>7036699</v>
+        <v>7036812</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,11 +1677,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1647,26 +1705,51 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138517</v>
+        <v>124120544</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,37 +1762,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436623</v>
+        <v>436449</v>
       </c>
       <c r="R11" t="n">
-        <v>7036558</v>
+        <v>7036726</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1736,11 +1819,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1749,30 +1842,55 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138492</v>
+        <v>124122815</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1781,16 +1899,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1799,19 +1917,29 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436577</v>
+        <v>436455</v>
       </c>
       <c r="R12" t="n">
-        <v>7036686</v>
+        <v>7036885</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1838,14 +1966,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,26 +1989,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124122388</v>
+        <v>124138486</v>
       </c>
       <c r="B13" t="n">
-        <v>57942</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,56 +2026,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436519</v>
+        <v>436686</v>
       </c>
       <c r="R13" t="n">
-        <v>7036935</v>
+        <v>7036815</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1964,21 +2083,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1987,31 +2096,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122460</v>
+        <v>124138527</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2024,48 +2128,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436516</v>
+        <v>436655</v>
       </c>
       <c r="R14" t="n">
-        <v>7036958</v>
+        <v>7036737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2095,26 +2185,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2123,31 +2198,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124120889</v>
+        <v>124138524</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,39 +2230,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436483</v>
+        <v>436539</v>
       </c>
       <c r="R15" t="n">
-        <v>7036812</v>
+        <v>7036496</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,26 +2287,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2250,51 +2300,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124121048</v>
+        <v>124122264</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,31 +2328,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2336,13 +2375,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436428</v>
+        <v>436515</v>
       </c>
       <c r="R16" t="n">
-        <v>7036785</v>
+        <v>7036863</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2369,21 +2408,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2396,26 +2425,6 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2433,14 +2442,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124138500</v>
+        <v>124121529</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2449,37 +2458,56 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436566</v>
+        <v>436390</v>
       </c>
       <c r="R17" t="n">
-        <v>7036478</v>
+        <v>7036767</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2506,14 +2534,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,26 +2562,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138522</v>
+        <v>124138487</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2556,21 +2599,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2580,10 +2623,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436590</v>
+        <v>436511</v>
       </c>
       <c r="R18" t="n">
-        <v>7036784</v>
+        <v>7036406</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2642,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138486</v>
+        <v>124138516</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,25 +2697,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2682,10 +2725,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436686</v>
+        <v>436629</v>
       </c>
       <c r="R19" t="n">
-        <v>7036815</v>
+        <v>7036589</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2744,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124138487</v>
+        <v>124123667</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,37 +2803,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436511</v>
+        <v>436566</v>
       </c>
       <c r="R20" t="n">
-        <v>7036406</v>
+        <v>7036880</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2817,11 +2865,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2830,30 +2893,55 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138494</v>
+        <v>124121014</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2862,37 +2950,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436665</v>
+        <v>436440</v>
       </c>
       <c r="R21" t="n">
-        <v>7036654</v>
+        <v>7036807</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2919,14 +3007,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2937,30 +3030,55 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138497</v>
+        <v>124121853</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2969,37 +3087,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436619</v>
+        <v>436611</v>
       </c>
       <c r="R22" t="n">
-        <v>7036576</v>
+        <v>7036804</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3026,14 +3144,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3044,26 +3172,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124121762</v>
+        <v>124138529</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3076,37 +3229,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436547</v>
+        <v>436661</v>
       </c>
       <c r="R23" t="n">
-        <v>7036757</v>
+        <v>7036719</v>
       </c>
       <c r="S23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3133,21 +3286,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3156,51 +3299,26 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138518</v>
+        <v>124120678</v>
       </c>
       <c r="B24" t="n">
-        <v>57883</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3209,45 +3327,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436552</v>
+        <v>436489</v>
       </c>
       <c r="R24" t="n">
-        <v>7036703</v>
+        <v>7036772</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3274,11 +3393,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3287,26 +3421,51 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124120678</v>
+        <v>124138514</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,42 +3478,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436489</v>
+        <v>436467</v>
       </c>
       <c r="R25" t="n">
-        <v>7036772</v>
+        <v>7036669</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3381,24 +3535,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3409,48 +3553,23 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124121014</v>
+        <v>124138531</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3486,17 +3605,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436440</v>
+        <v>436554</v>
       </c>
       <c r="R26" t="n">
-        <v>7036807</v>
+        <v>7036548</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3523,19 +3642,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3546,48 +3660,23 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124121853</v>
+        <v>124121762</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3627,13 +3716,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436611</v>
+        <v>436547</v>
       </c>
       <c r="R27" t="n">
-        <v>7036804</v>
+        <v>7036757</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3662,7 +3751,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3672,12 +3761,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3729,10 +3813,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138534</v>
+        <v>124121048</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3745,37 +3829,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436665</v>
+        <v>436428</v>
       </c>
       <c r="R28" t="n">
-        <v>7036708</v>
+        <v>7036785</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3802,11 +3891,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3815,26 +3914,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124122264</v>
+        <v>124123595</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3843,60 +3967,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436515</v>
+        <v>436560</v>
       </c>
       <c r="R29" t="n">
-        <v>7036863</v>
+        <v>7036869</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3923,11 +4028,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3940,6 +4055,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3957,53 +4092,58 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138490</v>
+        <v>124120703</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436542</v>
+        <v>436492</v>
       </c>
       <c r="R30" t="n">
-        <v>7036748</v>
+        <v>7036774</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4030,14 +4170,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,26 +4198,51 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124121529</v>
+        <v>124138484</v>
       </c>
       <c r="B31" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4080,56 +4255,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436390</v>
+        <v>436524</v>
       </c>
       <c r="R31" t="n">
-        <v>7036767</v>
+        <v>7036571</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4156,26 +4312,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4184,31 +4325,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138519</v>
+        <v>124122388</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>57942</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4221,37 +4357,56 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436513</v>
+        <v>436519</v>
       </c>
       <c r="R32" t="n">
-        <v>7036741</v>
+        <v>7036935</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4278,11 +4433,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4291,26 +4456,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124124067</v>
+        <v>124122426</v>
       </c>
       <c r="B33" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4323,42 +4493,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436566</v>
+        <v>436497</v>
       </c>
       <c r="R33" t="n">
-        <v>7036754</v>
+        <v>7036929</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4387,7 +4552,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4397,7 +4562,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4426,12 +4591,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4449,10 +4614,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124120467</v>
+        <v>124138508</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4465,21 +4630,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4487,16 +4652,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4504,17 +4662,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436380</v>
+        <v>436630</v>
       </c>
       <c r="R34" t="n">
-        <v>7036719</v>
+        <v>7036552</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4541,21 +4699,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4564,31 +4712,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138524</v>
+        <v>124138511</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4601,34 +4744,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436539</v>
+        <v>436582</v>
       </c>
       <c r="R35" t="n">
-        <v>7036496</v>
+        <v>7036714</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4687,10 +4842,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124138531</v>
+        <v>124120741</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4703,37 +4858,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436554</v>
+        <v>436483</v>
       </c>
       <c r="R36" t="n">
-        <v>7036548</v>
+        <v>7036788</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4760,14 +4920,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4778,26 +4943,51 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124123595</v>
+        <v>124138521</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4810,37 +5000,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436560</v>
+        <v>436548</v>
       </c>
       <c r="R37" t="n">
-        <v>7036869</v>
+        <v>7036699</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4867,21 +5057,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:51</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4890,51 +5070,26 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138516</v>
+        <v>124138535</v>
       </c>
       <c r="B38" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4943,25 +5098,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4971,10 +5126,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436629</v>
+        <v>436609</v>
       </c>
       <c r="R38" t="n">
-        <v>7036589</v>
+        <v>7036617</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5033,14 +5188,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138489</v>
+        <v>124124067</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5049,34 +5204,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436553</v>
+        <v>436566</v>
       </c>
       <c r="R39" t="n">
-        <v>7036719</v>
+        <v>7036754</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5106,14 +5266,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5124,26 +5289,51 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124120741</v>
+        <v>124122460</v>
       </c>
       <c r="B40" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5156,27 +5346,36 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5185,13 +5384,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436483</v>
+        <v>436516</v>
       </c>
       <c r="R40" t="n">
-        <v>7036788</v>
+        <v>7036958</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5220,7 +5419,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5230,7 +5429,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5245,26 +5449,6 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5282,10 +5466,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124120703</v>
+        <v>124138519</v>
       </c>
       <c r="B41" t="n">
-        <v>79927</v>
+        <v>91030</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5294,46 +5478,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436492</v>
+        <v>436513</v>
       </c>
       <c r="R41" t="n">
-        <v>7036774</v>
+        <v>7036741</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5360,26 +5539,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5388,48 +5552,23 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138535</v>
+        <v>124124670</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5465,17 +5604,17 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436609</v>
+        <v>436446</v>
       </c>
       <c r="R42" t="n">
-        <v>7036617</v>
+        <v>7036676</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5502,11 +5641,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5515,48 +5664,73 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124123983</v>
+        <v>124120467</v>
       </c>
       <c r="B43" t="n">
-        <v>57513</v>
+        <v>57883</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5564,10 +5738,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5576,13 +5764,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436575</v>
+        <v>436380</v>
       </c>
       <c r="R43" t="n">
-        <v>7036750</v>
+        <v>7036719</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5611,7 +5799,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5621,12 +5809,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5641,26 +5824,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5678,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138499</v>
+        <v>124138497</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5718,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436565</v>
+        <v>436619</v>
       </c>
       <c r="R44" t="n">
-        <v>7036491</v>
+        <v>7036576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5785,14 +5948,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138511</v>
+        <v>124138502</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5801,46 +5964,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436582</v>
+        <v>436558</v>
       </c>
       <c r="R45" t="n">
-        <v>7036714</v>
+        <v>7036469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5873,6 +6032,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5899,14 +6063,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124122426</v>
+        <v>124123983</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5915,37 +6079,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436497</v>
+        <v>436575</v>
       </c>
       <c r="R46" t="n">
-        <v>7036929</v>
+        <v>7036750</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5974,7 +6143,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5984,7 +6153,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6013,12 +6187,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6036,14 +6210,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124119822</v>
+        <v>124138490</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6052,37 +6226,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436287</v>
+        <v>436542</v>
       </c>
       <c r="R47" t="n">
-        <v>7036648</v>
+        <v>7036748</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6114,6 +6288,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -6122,55 +6301,30 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124122815</v>
+        <v>124138494</v>
       </c>
       <c r="B48" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6179,16 +6333,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6197,29 +6351,19 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436455</v>
+        <v>436665</v>
       </c>
       <c r="R48" t="n">
-        <v>7036885</v>
+        <v>7036654</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6246,19 +6390,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6269,35 +6408,30 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138527</v>
+        <v>124138492</v>
       </c>
       <c r="B49" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6306,21 +6440,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6330,10 +6464,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436655</v>
+        <v>436577</v>
       </c>
       <c r="R49" t="n">
-        <v>7036737</v>
+        <v>7036686</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6366,6 +6500,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6392,55 +6531,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124124271</v>
+        <v>124138500</v>
       </c>
       <c r="B50" t="n">
-        <v>91700</v>
+        <v>57513</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436563</v>
+        <v>436566</v>
       </c>
       <c r="R50" t="n">
-        <v>7036748</v>
+        <v>7036478</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6470,19 +6604,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:07</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6493,55 +6622,30 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124120544</v>
+        <v>124138505</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6550,37 +6654,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436449</v>
+        <v>436515</v>
       </c>
       <c r="R51" t="n">
-        <v>7036726</v>
+        <v>7036414</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6607,19 +6711,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:19</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6630,55 +6729,30 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124123667</v>
+        <v>124138489</v>
       </c>
       <c r="B52" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6687,16 +6761,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6705,24 +6779,19 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436566</v>
+        <v>436553</v>
       </c>
       <c r="R52" t="n">
-        <v>7036880</v>
+        <v>7036719</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6749,24 +6818,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6777,55 +6836,30 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124122092</v>
+        <v>124138499</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6834,53 +6868,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436572</v>
+        <v>436565</v>
       </c>
       <c r="R53" t="n">
-        <v>7036828</v>
+        <v>7036491</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6910,24 +6925,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6938,21 +6943,16 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124122092</v>
+        <v>124120678</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -734,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436572</v>
+        <v>436489</v>
       </c>
       <c r="R2" t="n">
-        <v>7036828</v>
+        <v>7036772</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,6 +785,26 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,7 +822,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138525</v>
+        <v>124120741</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -850,19 +856,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436632</v>
+        <v>436483</v>
       </c>
       <c r="R3" t="n">
-        <v>7036740</v>
+        <v>7036788</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,11 +900,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -902,26 +923,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138517</v>
+        <v>124138511</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +980,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436623</v>
+        <v>436582</v>
       </c>
       <c r="R4" t="n">
-        <v>7036558</v>
+        <v>7036714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,10 +1078,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138518</v>
+        <v>124120703</v>
       </c>
       <c r="B5" t="n">
-        <v>57883</v>
+        <v>79927</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,41 +1094,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436552</v>
+        <v>436492</v>
       </c>
       <c r="R5" t="n">
-        <v>7036703</v>
+        <v>7036774</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,11 +1156,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1110,26 +1184,51 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124119822</v>
+        <v>124138525</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,37 +1241,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436287</v>
+        <v>436632</v>
       </c>
       <c r="R6" t="n">
-        <v>7036648</v>
+        <v>7036740</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,41 +1311,16 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1355,10 +1429,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124138522</v>
+        <v>124124670</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,37 +1445,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436590</v>
+        <v>436446</v>
       </c>
       <c r="R8" t="n">
-        <v>7036784</v>
+        <v>7036676</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1428,11 +1502,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1441,26 +1525,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124124271</v>
+        <v>124123595</v>
       </c>
       <c r="B9" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,46 +1578,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436563</v>
+        <v>436560</v>
       </c>
       <c r="R9" t="n">
-        <v>7036748</v>
+        <v>7036869</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1537,7 +1641,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1651,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,12 +1680,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1599,7 +1703,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124120889</v>
+        <v>124123667</v>
       </c>
       <c r="B10" t="n">
         <v>57529</v>
@@ -1635,7 +1739,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1644,13 +1748,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436483</v>
+        <v>436566</v>
       </c>
       <c r="R10" t="n">
-        <v>7036812</v>
+        <v>7036880</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1679,7 +1783,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1793,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1746,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124120544</v>
+        <v>124138521</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1762,37 +1866,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436449</v>
+        <v>436548</v>
       </c>
       <c r="R11" t="n">
-        <v>7036726</v>
+        <v>7036699</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,21 +1923,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:19</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1842,51 +1936,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124122815</v>
+        <v>124121762</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,47 +1968,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436455</v>
+        <v>436547</v>
       </c>
       <c r="R12" t="n">
-        <v>7036885</v>
+        <v>7036757</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1968,7 +2027,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,7 +2037,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1993,6 +2052,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2010,10 +2089,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124138486</v>
+        <v>124120889</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2026,34 +2105,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436686</v>
+        <v>436483</v>
       </c>
       <c r="R13" t="n">
-        <v>7036815</v>
+        <v>7036812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,11 +2167,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2096,26 +2195,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124138527</v>
+        <v>124122388</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>57942</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,37 +2252,56 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436655</v>
+        <v>436519</v>
       </c>
       <c r="R14" t="n">
-        <v>7036737</v>
+        <v>7036935</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2185,11 +2328,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2198,26 +2351,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138524</v>
+        <v>124138517</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2230,21 +2388,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2254,10 +2412,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436539</v>
+        <v>436623</v>
       </c>
       <c r="R15" t="n">
-        <v>7036496</v>
+        <v>7036558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2442,7 +2600,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124121529</v>
+        <v>124122460</v>
       </c>
       <c r="B17" t="n">
         <v>57666</v>
@@ -2480,14 +2638,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2501,13 +2654,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436390</v>
+        <v>436516</v>
       </c>
       <c r="R17" t="n">
-        <v>7036767</v>
+        <v>7036958</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2536,7 +2689,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2699,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2583,10 +2736,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138487</v>
+        <v>124138519</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2599,21 +2752,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2623,10 +2776,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436511</v>
+        <v>436513</v>
       </c>
       <c r="R18" t="n">
-        <v>7036406</v>
+        <v>7036741</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2787,10 +2940,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124123667</v>
+        <v>124121529</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,27 +2956,41 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2832,13 +2999,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436566</v>
+        <v>436390</v>
       </c>
       <c r="R20" t="n">
-        <v>7036880</v>
+        <v>7036767</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,7 +3034,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2877,12 +3044,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,26 +3064,6 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2934,7 +3081,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124121014</v>
+        <v>124138531</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2970,17 +3117,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436440</v>
+        <v>436554</v>
       </c>
       <c r="R21" t="n">
-        <v>7036807</v>
+        <v>7036548</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3007,19 +3154,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:35</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3030,51 +3172,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124121853</v>
+        <v>124138529</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3087,37 +3204,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436611</v>
+        <v>436661</v>
       </c>
       <c r="R22" t="n">
-        <v>7036804</v>
+        <v>7036719</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3144,26 +3261,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3172,51 +3274,26 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138529</v>
+        <v>124138514</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3229,21 +3306,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3253,10 +3330,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436661</v>
+        <v>436467</v>
       </c>
       <c r="R23" t="n">
-        <v>7036719</v>
+        <v>7036669</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3289,6 +3366,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3315,10 +3397,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124120678</v>
+        <v>124138487</v>
       </c>
       <c r="B24" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3331,42 +3413,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436489</v>
+        <v>436511</v>
       </c>
       <c r="R24" t="n">
-        <v>7036772</v>
+        <v>7036406</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3393,26 +3470,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3421,51 +3483,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138514</v>
+        <v>124121048</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3478,37 +3515,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436467</v>
+        <v>436428</v>
       </c>
       <c r="R25" t="n">
-        <v>7036669</v>
+        <v>7036785</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3535,14 +3577,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3553,26 +3600,51 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138531</v>
+        <v>124138508</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3581,38 +3653,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436554</v>
+        <v>436630</v>
       </c>
       <c r="R26" t="n">
-        <v>7036548</v>
+        <v>7036552</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3645,11 +3729,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3676,7 +3755,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124121762</v>
+        <v>124121853</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3716,13 +3795,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436547</v>
+        <v>436611</v>
       </c>
       <c r="R27" t="n">
-        <v>7036757</v>
+        <v>7036804</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3751,7 +3830,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3761,7 +3840,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3813,10 +3897,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124121048</v>
+        <v>124138486</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3829,42 +3913,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436428</v>
+        <v>436686</v>
       </c>
       <c r="R28" t="n">
-        <v>7036785</v>
+        <v>7036815</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3891,21 +3970,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3914,51 +3983,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124123595</v>
+        <v>124124067</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3971,37 +4015,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436560</v>
+        <v>436566</v>
       </c>
       <c r="R29" t="n">
-        <v>7036869</v>
+        <v>7036754</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4030,7 +4079,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4040,7 +4089,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4069,12 +4118,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4092,10 +4141,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124120703</v>
+        <v>124124271</v>
       </c>
       <c r="B30" t="n">
-        <v>79927</v>
+        <v>91700</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4108,27 +4157,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4137,13 +4186,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436492</v>
+        <v>436563</v>
       </c>
       <c r="R30" t="n">
-        <v>7036774</v>
+        <v>7036748</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4172,7 +4221,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4182,12 +4231,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,22 +4250,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4239,10 +4283,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124138484</v>
+        <v>124120544</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4255,37 +4299,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436524</v>
+        <v>436449</v>
       </c>
       <c r="R31" t="n">
-        <v>7036571</v>
+        <v>7036726</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4312,11 +4356,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4325,26 +4379,51 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124122388</v>
+        <v>124138527</v>
       </c>
       <c r="B32" t="n">
-        <v>57942</v>
+        <v>91030</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4357,56 +4436,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103001</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436519</v>
+        <v>436655</v>
       </c>
       <c r="R32" t="n">
-        <v>7036935</v>
+        <v>7036737</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4433,21 +4493,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4456,31 +4506,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124122426</v>
+        <v>124122092</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4493,37 +4538,56 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436497</v>
+        <v>436572</v>
       </c>
       <c r="R33" t="n">
-        <v>7036929</v>
+        <v>7036828</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4552,7 +4616,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4562,7 +4626,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4577,26 +4646,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4614,10 +4663,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138508</v>
+        <v>124120467</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>57883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4630,21 +4679,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4652,9 +4701,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4662,17 +4718,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436630</v>
+        <v>436380</v>
       </c>
       <c r="R34" t="n">
-        <v>7036552</v>
+        <v>7036719</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4699,11 +4755,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4712,26 +4778,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138511</v>
+        <v>124138518</v>
       </c>
       <c r="B35" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4740,50 +4811,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436582</v>
+        <v>436552</v>
       </c>
       <c r="R35" t="n">
-        <v>7036714</v>
+        <v>7036703</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4842,10 +4905,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124120741</v>
+        <v>124119822</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4858,42 +4921,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436483</v>
+        <v>436287</v>
       </c>
       <c r="R36" t="n">
-        <v>7036788</v>
+        <v>7036648</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4920,21 +4978,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4961,12 +5009,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4984,10 +5032,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124138521</v>
+        <v>124121014</v>
       </c>
       <c r="B37" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5000,37 +5048,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436548</v>
+        <v>436440</v>
       </c>
       <c r="R37" t="n">
-        <v>7036699</v>
+        <v>7036807</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5057,11 +5105,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5070,26 +5128,51 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138535</v>
+        <v>124138522</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5102,21 +5185,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5126,10 +5209,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436609</v>
+        <v>436590</v>
       </c>
       <c r="R38" t="n">
-        <v>7036617</v>
+        <v>7036784</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5188,10 +5271,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124124067</v>
+        <v>124138524</v>
       </c>
       <c r="B39" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5204,39 +5287,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436566</v>
+        <v>436539</v>
       </c>
       <c r="R39" t="n">
-        <v>7036754</v>
+        <v>7036496</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5266,21 +5344,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5289,51 +5357,26 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122460</v>
+        <v>124122426</v>
       </c>
       <c r="B40" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5346,51 +5389,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436516</v>
+        <v>436497</v>
       </c>
       <c r="R40" t="n">
-        <v>7036958</v>
+        <v>7036929</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5419,7 +5448,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5429,12 +5458,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5449,6 +5473,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5466,10 +5510,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138519</v>
+        <v>124138484</v>
       </c>
       <c r="B41" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5482,21 +5526,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5506,10 +5550,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436513</v>
+        <v>436524</v>
       </c>
       <c r="R41" t="n">
-        <v>7036741</v>
+        <v>7036571</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5568,10 +5612,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124124670</v>
+        <v>124122815</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5584,37 +5628,47 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436446</v>
+        <v>436455</v>
       </c>
       <c r="R42" t="n">
-        <v>7036676</v>
+        <v>7036885</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5643,7 +5697,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5653,7 +5707,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5668,26 +5722,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5705,10 +5739,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124120467</v>
+        <v>124138535</v>
       </c>
       <c r="B43" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5717,60 +5751,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436380</v>
+        <v>436609</v>
       </c>
       <c r="R43" t="n">
-        <v>7036719</v>
+        <v>7036617</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5797,21 +5812,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5820,28 +5825,23 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138497</v>
+        <v>124138490</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436619</v>
+        <v>436542</v>
       </c>
       <c r="R44" t="n">
-        <v>7036576</v>
+        <v>7036748</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124123983</v>
+        <v>124138500</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6097,21 +6097,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436575</v>
+        <v>436566</v>
       </c>
       <c r="R46" t="n">
-        <v>7036750</v>
+        <v>7036478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6141,24 +6136,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6169,48 +6154,23 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138490</v>
+        <v>124138505</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6250,10 +6210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436542</v>
+        <v>436515</v>
       </c>
       <c r="R47" t="n">
-        <v>7036748</v>
+        <v>7036414</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6290,7 +6250,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6317,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138494</v>
+        <v>124138492</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6357,10 +6317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436665</v>
+        <v>436577</v>
       </c>
       <c r="R48" t="n">
-        <v>7036654</v>
+        <v>7036686</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6397,7 +6357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6424,7 +6384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138492</v>
+        <v>124138489</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6464,10 +6424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436577</v>
+        <v>436553</v>
       </c>
       <c r="R49" t="n">
-        <v>7036686</v>
+        <v>7036719</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6531,7 +6491,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138500</v>
+        <v>124138499</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6571,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436566</v>
+        <v>436565</v>
       </c>
       <c r="R50" t="n">
-        <v>7036478</v>
+        <v>7036491</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6638,7 +6598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138505</v>
+        <v>124138494</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6678,10 +6638,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436515</v>
+        <v>436665</v>
       </c>
       <c r="R51" t="n">
-        <v>7036414</v>
+        <v>7036654</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6718,7 +6678,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,7 +6705,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138489</v>
+        <v>124123983</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6779,16 +6739,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436553</v>
+        <v>436575</v>
       </c>
       <c r="R52" t="n">
-        <v>7036719</v>
+        <v>7036750</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6818,14 +6783,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6836,23 +6811,48 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138499</v>
+        <v>124138497</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436565</v>
+        <v>436619</v>
       </c>
       <c r="R53" t="n">
-        <v>7036491</v>
+        <v>7036576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124138521</v>
+        <v>124121762</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,37 +1866,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436548</v>
+        <v>436547</v>
       </c>
       <c r="R11" t="n">
-        <v>7036699</v>
+        <v>7036757</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1923,11 +1923,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1936,26 +1946,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124121762</v>
+        <v>124138521</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1968,37 +2003,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436547</v>
+        <v>436548</v>
       </c>
       <c r="R12" t="n">
-        <v>7036757</v>
+        <v>7036699</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2025,21 +2060,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2048,41 +2073,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -822,7 +822,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124120741</v>
+        <v>124138521</v>
       </c>
       <c r="B3" t="n">
         <v>91030</v>
@@ -856,24 +856,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436483</v>
+        <v>436548</v>
       </c>
       <c r="R3" t="n">
-        <v>7036788</v>
+        <v>7036699</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,21 +895,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:26</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,51 +908,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124138511</v>
+        <v>124120467</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57883</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -976,35 +936,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1012,17 +979,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436582</v>
+        <v>436380</v>
       </c>
       <c r="R4" t="n">
-        <v>7036714</v>
+        <v>7036719</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1049,11 +1016,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1062,26 +1039,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124120703</v>
+        <v>124138529</v>
       </c>
       <c r="B5" t="n">
-        <v>79927</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1090,46 +1072,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436492</v>
+        <v>436661</v>
       </c>
       <c r="R5" t="n">
-        <v>7036774</v>
+        <v>7036719</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1156,26 +1133,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,51 +1146,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124138525</v>
+        <v>124138487</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1241,21 +1178,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1265,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436632</v>
+        <v>436511</v>
       </c>
       <c r="R6" t="n">
-        <v>7036740</v>
+        <v>7036406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1327,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138534</v>
+        <v>124138508</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1339,38 +1276,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436665</v>
+        <v>436630</v>
       </c>
       <c r="R7" t="n">
-        <v>7036708</v>
+        <v>7036552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1429,7 +1378,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124124670</v>
+        <v>124123595</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1469,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436446</v>
+        <v>436560</v>
       </c>
       <c r="R8" t="n">
-        <v>7036676</v>
+        <v>7036869</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1504,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1514,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1543,12 +1492,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1566,10 +1515,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124123595</v>
+        <v>124121529</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1582,37 +1531,56 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436560</v>
+        <v>436390</v>
       </c>
       <c r="R9" t="n">
-        <v>7036869</v>
+        <v>7036767</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1641,7 +1609,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1651,7 +1619,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1666,26 +1639,6 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1850,10 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124121762</v>
+        <v>124120889</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1866,37 +1819,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436547</v>
+        <v>436483</v>
       </c>
       <c r="R11" t="n">
-        <v>7036757</v>
+        <v>7036812</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,7 +1883,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,7 +1893,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,12 +1927,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1987,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138521</v>
+        <v>124138514</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,21 +1966,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -2027,10 +1990,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436548</v>
+        <v>436467</v>
       </c>
       <c r="R12" t="n">
-        <v>7036699</v>
+        <v>7036669</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2063,6 +2026,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,10 +2057,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124120889</v>
+        <v>124138531</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2105,39 +2073,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436483</v>
+        <v>436554</v>
       </c>
       <c r="R13" t="n">
-        <v>7036812</v>
+        <v>7036548</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2167,24 +2130,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hackspår i stambasen.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2195,51 +2148,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122388</v>
+        <v>124122426</v>
       </c>
       <c r="B14" t="n">
-        <v>57942</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,56 +2180,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436519</v>
+        <v>436497</v>
       </c>
       <c r="R14" t="n">
-        <v>7036935</v>
+        <v>7036929</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2330,7 +2239,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2340,7 +2249,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2355,6 +2264,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2372,10 +2301,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124138517</v>
+        <v>124120741</v>
       </c>
       <c r="B15" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2388,37 +2317,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436623</v>
+        <v>436483</v>
       </c>
       <c r="R15" t="n">
-        <v>7036558</v>
+        <v>7036788</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2445,11 +2379,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2458,26 +2402,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124122264</v>
+        <v>124138535</v>
       </c>
       <c r="B16" t="n">
-        <v>57883</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2486,60 +2455,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436515</v>
+        <v>436609</v>
       </c>
       <c r="R16" t="n">
-        <v>7036863</v>
+        <v>7036617</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2579,28 +2529,23 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124122460</v>
+        <v>124122092</v>
       </c>
       <c r="B17" t="n">
         <v>57666</v>
@@ -2638,9 +2583,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2654,10 +2604,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436516</v>
+        <v>436572</v>
       </c>
       <c r="R17" t="n">
-        <v>7036958</v>
+        <v>7036828</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2689,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2699,12 +2649,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2736,10 +2686,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138519</v>
+        <v>124138517</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>91299</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2752,21 +2702,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2776,10 +2726,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436513</v>
+        <v>436623</v>
       </c>
       <c r="R18" t="n">
-        <v>7036741</v>
+        <v>7036558</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2838,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124138516</v>
+        <v>124120703</v>
       </c>
       <c r="B19" t="n">
-        <v>91457</v>
+        <v>79927</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2850,41 +2800,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436629</v>
+        <v>436492</v>
       </c>
       <c r="R19" t="n">
-        <v>7036589</v>
+        <v>7036774</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2911,11 +2866,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2924,26 +2894,51 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124121529</v>
+        <v>124124670</v>
       </c>
       <c r="B20" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2956,56 +2951,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436390</v>
+        <v>436446</v>
       </c>
       <c r="R20" t="n">
-        <v>7036767</v>
+        <v>7036676</v>
       </c>
       <c r="S20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3034,7 +3010,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3044,12 +3020,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3064,6 +3035,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3081,10 +3072,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124138531</v>
+        <v>124124271</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3093,38 +3084,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436554</v>
+        <v>436563</v>
       </c>
       <c r="R21" t="n">
-        <v>7036548</v>
+        <v>7036748</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3154,14 +3150,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3172,26 +3173,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124138529</v>
+        <v>124119822</v>
       </c>
       <c r="B22" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3204,37 +3230,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436661</v>
+        <v>436287</v>
       </c>
       <c r="R22" t="n">
-        <v>7036719</v>
+        <v>7036648</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3274,26 +3300,51 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138514</v>
+        <v>124138519</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3306,21 +3357,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3330,10 +3381,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436467</v>
+        <v>436513</v>
       </c>
       <c r="R23" t="n">
-        <v>7036669</v>
+        <v>7036741</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3366,11 +3417,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3397,10 +3443,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124138487</v>
+        <v>124122388</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57942</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3413,37 +3459,56 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436511</v>
+        <v>436519</v>
       </c>
       <c r="R24" t="n">
-        <v>7036406</v>
+        <v>7036935</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3470,11 +3535,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3483,26 +3558,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124121048</v>
+        <v>124138518</v>
       </c>
       <c r="B25" t="n">
-        <v>91030</v>
+        <v>57883</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3511,46 +3591,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436428</v>
+        <v>436552</v>
       </c>
       <c r="R25" t="n">
-        <v>7036785</v>
+        <v>7036703</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3577,21 +3656,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3600,51 +3669,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138508</v>
+        <v>124138486</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3653,50 +3697,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436630</v>
+        <v>436686</v>
       </c>
       <c r="R26" t="n">
-        <v>7036552</v>
+        <v>7036815</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3755,10 +3787,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124121853</v>
+        <v>124138484</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3771,37 +3803,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436611</v>
+        <v>436524</v>
       </c>
       <c r="R27" t="n">
-        <v>7036804</v>
+        <v>7036571</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3828,26 +3860,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3856,51 +3873,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124138486</v>
+        <v>124121048</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3913,37 +3905,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436686</v>
+        <v>436428</v>
       </c>
       <c r="R28" t="n">
-        <v>7036815</v>
+        <v>7036785</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3970,11 +3967,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3983,26 +3990,51 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124124067</v>
+        <v>124138527</v>
       </c>
       <c r="B29" t="n">
-        <v>91008</v>
+        <v>91030</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4015,39 +4047,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436566</v>
+        <v>436655</v>
       </c>
       <c r="R29" t="n">
-        <v>7036754</v>
+        <v>7036737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4077,21 +4104,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4100,51 +4117,26 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124124271</v>
+        <v>124138534</v>
       </c>
       <c r="B30" t="n">
-        <v>91700</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4153,43 +4145,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436563</v>
+        <v>436665</v>
       </c>
       <c r="R30" t="n">
-        <v>7036748</v>
+        <v>7036708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4219,21 +4206,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4242,51 +4219,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124120544</v>
+        <v>124124067</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4299,37 +4251,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436449</v>
+        <v>436566</v>
       </c>
       <c r="R31" t="n">
-        <v>7036726</v>
+        <v>7036754</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4358,7 +4315,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4368,7 +4325,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4397,12 +4354,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4420,10 +4377,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124138527</v>
+        <v>124122815</v>
       </c>
       <c r="B32" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4436,37 +4393,47 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436655</v>
+        <v>436455</v>
       </c>
       <c r="R32" t="n">
-        <v>7036737</v>
+        <v>7036885</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4493,11 +4460,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4506,26 +4483,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124122092</v>
+        <v>124121762</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4538,56 +4520,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436572</v>
+        <v>436547</v>
       </c>
       <c r="R33" t="n">
-        <v>7036828</v>
+        <v>7036757</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4616,7 +4579,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4626,12 +4589,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4646,6 +4604,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4663,10 +4641,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124120467</v>
+        <v>124138524</v>
       </c>
       <c r="B34" t="n">
-        <v>57883</v>
+        <v>91030</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4675,60 +4653,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436380</v>
+        <v>436539</v>
       </c>
       <c r="R34" t="n">
-        <v>7036719</v>
+        <v>7036496</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4755,21 +4714,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4778,28 +4727,23 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124138518</v>
+        <v>124122264</v>
       </c>
       <c r="B35" t="n">
         <v>57883</v>
@@ -4832,24 +4776,39 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436552</v>
+        <v>436515</v>
       </c>
       <c r="R35" t="n">
-        <v>7036703</v>
+        <v>7036863</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4889,23 +4848,28 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124119822</v>
+        <v>124121853</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4945,10 +4909,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436287</v>
+        <v>436611</v>
       </c>
       <c r="R36" t="n">
-        <v>7036648</v>
+        <v>7036804</v>
       </c>
       <c r="S36" t="n">
         <v>8</v>
@@ -4978,9 +4942,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5032,10 +5011,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124121014</v>
+        <v>124122460</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5048,37 +5027,51 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436440</v>
+        <v>436516</v>
       </c>
       <c r="R37" t="n">
-        <v>7036807</v>
+        <v>7036958</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5107,7 +5100,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5117,7 +5110,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5132,26 +5130,6 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5169,10 +5147,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138522</v>
+        <v>124138511</v>
       </c>
       <c r="B38" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5185,34 +5163,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436590</v>
+        <v>436582</v>
       </c>
       <c r="R38" t="n">
-        <v>7036784</v>
+        <v>7036714</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5271,7 +5261,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138524</v>
+        <v>124138522</v>
       </c>
       <c r="B39" t="n">
         <v>91030</v>
@@ -5311,10 +5301,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436539</v>
+        <v>436590</v>
       </c>
       <c r="R39" t="n">
-        <v>7036496</v>
+        <v>7036784</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5373,10 +5363,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124122426</v>
+        <v>124138516</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91457</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5385,41 +5375,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436497</v>
+        <v>436629</v>
       </c>
       <c r="R40" t="n">
-        <v>7036929</v>
+        <v>7036589</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5446,21 +5436,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:17</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5469,51 +5449,26 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124138484</v>
+        <v>124121014</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5526,37 +5481,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436524</v>
+        <v>436440</v>
       </c>
       <c r="R41" t="n">
-        <v>7036571</v>
+        <v>7036807</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5583,11 +5538,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5596,26 +5561,51 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124122815</v>
+        <v>124138525</v>
       </c>
       <c r="B42" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5628,47 +5618,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436455</v>
+        <v>436632</v>
       </c>
       <c r="R42" t="n">
-        <v>7036885</v>
+        <v>7036740</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5695,21 +5675,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5718,28 +5688,23 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124138535</v>
+        <v>124120544</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5775,17 +5740,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436609</v>
+        <v>436449</v>
       </c>
       <c r="R43" t="n">
-        <v>7036617</v>
+        <v>7036726</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5812,11 +5777,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5825,23 +5800,48 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138490</v>
+        <v>124138500</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436542</v>
+        <v>436566</v>
       </c>
       <c r="R44" t="n">
-        <v>7036748</v>
+        <v>7036478</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6063,7 +6063,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138500</v>
+        <v>124138499</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436566</v>
+        <v>436565</v>
       </c>
       <c r="R46" t="n">
-        <v>7036478</v>
+        <v>7036491</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6277,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138492</v>
+        <v>124138494</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436577</v>
+        <v>436665</v>
       </c>
       <c r="R48" t="n">
-        <v>7036686</v>
+        <v>7036654</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,7 +6384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138489</v>
+        <v>124138492</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436553</v>
+        <v>436577</v>
       </c>
       <c r="R49" t="n">
-        <v>7036719</v>
+        <v>7036686</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138499</v>
+        <v>124138497</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436565</v>
+        <v>436619</v>
       </c>
       <c r="R50" t="n">
-        <v>7036491</v>
+        <v>7036576</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138494</v>
+        <v>124138489</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6638,10 +6638,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436665</v>
+        <v>436553</v>
       </c>
       <c r="R51" t="n">
-        <v>7036654</v>
+        <v>7036719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138497</v>
+        <v>124138490</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436619</v>
+        <v>436542</v>
       </c>
       <c r="R53" t="n">
-        <v>7036576</v>
+        <v>7036748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138500</v>
+        <v>124138489</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436566</v>
+        <v>436553</v>
       </c>
       <c r="R44" t="n">
-        <v>7036478</v>
+        <v>7036719</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138502</v>
+        <v>124138492</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5982,24 +5982,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436558</v>
+        <v>436577</v>
       </c>
       <c r="R45" t="n">
-        <v>7036469</v>
+        <v>7036686</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6036,7 +6028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6063,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138499</v>
+        <v>124138500</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6103,10 +6095,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436565</v>
+        <v>436566</v>
       </c>
       <c r="R46" t="n">
-        <v>7036491</v>
+        <v>7036478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6170,7 +6162,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138505</v>
+        <v>124138502</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6204,16 +6196,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436515</v>
+        <v>436558</v>
       </c>
       <c r="R47" t="n">
-        <v>7036414</v>
+        <v>7036469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138494</v>
+        <v>124138490</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6317,10 +6317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436665</v>
+        <v>436542</v>
       </c>
       <c r="R48" t="n">
-        <v>7036654</v>
+        <v>7036748</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,7 +6384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138492</v>
+        <v>124138499</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6424,10 +6424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436577</v>
+        <v>436565</v>
       </c>
       <c r="R49" t="n">
-        <v>7036686</v>
+        <v>7036491</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6491,7 +6491,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138497</v>
+        <v>124138505</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436619</v>
+        <v>436515</v>
       </c>
       <c r="R50" t="n">
-        <v>7036576</v>
+        <v>7036414</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6598,7 +6598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138489</v>
+        <v>124123983</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6632,16 +6632,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436553</v>
+        <v>436575</v>
       </c>
       <c r="R51" t="n">
-        <v>7036719</v>
+        <v>7036750</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6671,14 +6676,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6689,23 +6704,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124123983</v>
+        <v>124138494</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6739,21 +6779,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436575</v>
+        <v>436665</v>
       </c>
       <c r="R52" t="n">
-        <v>7036750</v>
+        <v>7036654</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6783,24 +6818,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6811,48 +6836,23 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138490</v>
+        <v>124138497</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436542</v>
+        <v>436619</v>
       </c>
       <c r="R53" t="n">
-        <v>7036748</v>
+        <v>7036576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138489</v>
+        <v>124138500</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436553</v>
+        <v>436566</v>
       </c>
       <c r="R44" t="n">
-        <v>7036719</v>
+        <v>7036478</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138492</v>
+        <v>124138494</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436577</v>
+        <v>436665</v>
       </c>
       <c r="R45" t="n">
-        <v>7036686</v>
+        <v>7036654</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138500</v>
+        <v>124138505</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436566</v>
+        <v>436515</v>
       </c>
       <c r="R46" t="n">
-        <v>7036478</v>
+        <v>7036414</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,7 +6162,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138502</v>
+        <v>124138497</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6196,24 +6196,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436558</v>
+        <v>436619</v>
       </c>
       <c r="R47" t="n">
-        <v>7036469</v>
+        <v>7036576</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6242,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6384,7 +6376,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138499</v>
+        <v>124123983</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6418,16 +6410,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436565</v>
+        <v>436575</v>
       </c>
       <c r="R49" t="n">
-        <v>7036491</v>
+        <v>7036750</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6457,14 +6454,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6475,23 +6482,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138505</v>
+        <v>124138492</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6531,10 +6563,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436515</v>
+        <v>436577</v>
       </c>
       <c r="R50" t="n">
-        <v>7036414</v>
+        <v>7036686</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6571,7 +6603,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6598,7 +6630,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124123983</v>
+        <v>124138489</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6632,21 +6664,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436575</v>
+        <v>436553</v>
       </c>
       <c r="R51" t="n">
-        <v>7036750</v>
+        <v>7036719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6676,24 +6703,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6704,48 +6721,23 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138494</v>
+        <v>124138502</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6779,16 +6771,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436665</v>
+        <v>436558</v>
       </c>
       <c r="R52" t="n">
-        <v>7036654</v>
+        <v>7036469</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138497</v>
+        <v>124138499</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436619</v>
+        <v>436565</v>
       </c>
       <c r="R53" t="n">
-        <v>7036576</v>
+        <v>7036491</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138500</v>
+        <v>124138492</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436566</v>
+        <v>436577</v>
       </c>
       <c r="R44" t="n">
-        <v>7036478</v>
+        <v>7036686</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138494</v>
+        <v>124138505</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436665</v>
+        <v>436515</v>
       </c>
       <c r="R45" t="n">
-        <v>7036654</v>
+        <v>7036414</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138505</v>
+        <v>124138502</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6089,16 +6089,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436515</v>
+        <v>436558</v>
       </c>
       <c r="R46" t="n">
-        <v>7036414</v>
+        <v>7036469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6135,7 +6143,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,7 +6170,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138497</v>
+        <v>124138490</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6202,10 +6210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436619</v>
+        <v>436542</v>
       </c>
       <c r="R47" t="n">
-        <v>7036576</v>
+        <v>7036748</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6269,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138490</v>
+        <v>124123983</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6303,16 +6311,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436542</v>
+        <v>436575</v>
       </c>
       <c r="R48" t="n">
-        <v>7036748</v>
+        <v>7036750</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6342,14 +6355,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6360,23 +6383,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124123983</v>
+        <v>124138489</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6410,21 +6458,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436575</v>
+        <v>436553</v>
       </c>
       <c r="R49" t="n">
-        <v>7036750</v>
+        <v>7036719</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6454,24 +6497,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6482,48 +6515,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138492</v>
+        <v>124138500</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6563,10 +6571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436577</v>
+        <v>436566</v>
       </c>
       <c r="R50" t="n">
-        <v>7036686</v>
+        <v>7036478</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6630,7 +6638,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138489</v>
+        <v>124138499</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6670,10 +6678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436553</v>
+        <v>436565</v>
       </c>
       <c r="R51" t="n">
-        <v>7036719</v>
+        <v>7036491</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6737,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138502</v>
+        <v>124138494</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6771,24 +6779,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436558</v>
+        <v>436665</v>
       </c>
       <c r="R52" t="n">
-        <v>7036469</v>
+        <v>7036654</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138499</v>
+        <v>124138497</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436565</v>
+        <v>436619</v>
       </c>
       <c r="R53" t="n">
-        <v>7036491</v>
+        <v>7036576</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138492</v>
+        <v>124138494</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436577</v>
+        <v>436665</v>
       </c>
       <c r="R44" t="n">
-        <v>7036686</v>
+        <v>7036654</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138505</v>
+        <v>124138497</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436515</v>
+        <v>436619</v>
       </c>
       <c r="R45" t="n">
-        <v>7036414</v>
+        <v>7036576</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138502</v>
+        <v>124138489</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6089,24 +6089,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436558</v>
+        <v>436553</v>
       </c>
       <c r="R46" t="n">
-        <v>7036469</v>
+        <v>7036719</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6143,7 +6135,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6170,7 +6162,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138490</v>
+        <v>124138502</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6204,16 +6196,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436542</v>
+        <v>436558</v>
       </c>
       <c r="R47" t="n">
-        <v>7036748</v>
+        <v>7036469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124123983</v>
+        <v>124138499</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6311,21 +6311,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436575</v>
+        <v>436565</v>
       </c>
       <c r="R48" t="n">
-        <v>7036750</v>
+        <v>7036491</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6355,24 +6350,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6383,48 +6368,23 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138489</v>
+        <v>124138500</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6464,10 +6424,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436553</v>
+        <v>436566</v>
       </c>
       <c r="R49" t="n">
-        <v>7036719</v>
+        <v>7036478</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6531,7 +6491,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138500</v>
+        <v>124138490</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6571,10 +6531,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436566</v>
+        <v>436542</v>
       </c>
       <c r="R50" t="n">
-        <v>7036478</v>
+        <v>7036748</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6638,7 +6598,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138499</v>
+        <v>124138492</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6678,10 +6638,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436565</v>
+        <v>436577</v>
       </c>
       <c r="R51" t="n">
-        <v>7036491</v>
+        <v>7036686</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6745,7 +6705,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138494</v>
+        <v>124123983</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6779,16 +6739,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436665</v>
+        <v>436575</v>
       </c>
       <c r="R52" t="n">
-        <v>7036654</v>
+        <v>7036750</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6818,14 +6783,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6836,23 +6811,48 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138497</v>
+        <v>124138505</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436619</v>
+        <v>436515</v>
       </c>
       <c r="R53" t="n">
-        <v>7036576</v>
+        <v>7036414</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138497</v>
+        <v>124138499</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436619</v>
+        <v>436565</v>
       </c>
       <c r="R45" t="n">
-        <v>7036576</v>
+        <v>7036491</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138489</v>
+        <v>124138500</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436553</v>
+        <v>436566</v>
       </c>
       <c r="R46" t="n">
-        <v>7036719</v>
+        <v>7036478</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138502</v>
+        <v>124138490</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6196,24 +6196,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436558</v>
+        <v>436542</v>
       </c>
       <c r="R47" t="n">
-        <v>7036469</v>
+        <v>7036748</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6242,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6269,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138499</v>
+        <v>124138492</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6317,10 +6309,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436565</v>
+        <v>436577</v>
       </c>
       <c r="R48" t="n">
-        <v>7036491</v>
+        <v>7036686</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6384,7 +6376,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138500</v>
+        <v>124123983</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6418,16 +6410,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436566</v>
+        <v>436575</v>
       </c>
       <c r="R49" t="n">
-        <v>7036478</v>
+        <v>7036750</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6457,14 +6454,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6475,23 +6482,48 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138490</v>
+        <v>124138502</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6525,16 +6557,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436542</v>
+        <v>436558</v>
       </c>
       <c r="R50" t="n">
-        <v>7036748</v>
+        <v>7036469</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6571,7 +6611,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6598,7 +6638,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138492</v>
+        <v>124138497</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6638,10 +6678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436577</v>
+        <v>436619</v>
       </c>
       <c r="R51" t="n">
-        <v>7036686</v>
+        <v>7036576</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6705,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124123983</v>
+        <v>124138489</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6739,21 +6779,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436575</v>
+        <v>436553</v>
       </c>
       <c r="R52" t="n">
-        <v>7036750</v>
+        <v>7036719</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6783,24 +6818,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6811,41 +6836,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138494</v>
+        <v>124138492</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436665</v>
+        <v>436577</v>
       </c>
       <c r="R44" t="n">
-        <v>7036654</v>
+        <v>7036686</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138499</v>
+        <v>124138500</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436565</v>
+        <v>436566</v>
       </c>
       <c r="R45" t="n">
-        <v>7036491</v>
+        <v>7036478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138500</v>
+        <v>124138505</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436566</v>
+        <v>436515</v>
       </c>
       <c r="R46" t="n">
-        <v>7036478</v>
+        <v>7036414</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,7 +6162,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138490</v>
+        <v>124138502</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6196,16 +6196,24 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436542</v>
+        <v>436558</v>
       </c>
       <c r="R47" t="n">
-        <v>7036748</v>
+        <v>7036469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6242,7 +6250,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6269,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138492</v>
+        <v>124138489</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6309,10 +6317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436577</v>
+        <v>436553</v>
       </c>
       <c r="R48" t="n">
-        <v>7036686</v>
+        <v>7036719</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6523,7 +6531,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138502</v>
+        <v>124138490</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6557,24 +6565,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436558</v>
+        <v>436542</v>
       </c>
       <c r="R50" t="n">
-        <v>7036469</v>
+        <v>7036748</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6745,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138489</v>
+        <v>124138494</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436553</v>
+        <v>436665</v>
       </c>
       <c r="R52" t="n">
-        <v>7036719</v>
+        <v>7036654</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138505</v>
+        <v>124138499</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436515</v>
+        <v>436565</v>
       </c>
       <c r="R53" t="n">
-        <v>7036414</v>
+        <v>7036491</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138492</v>
+        <v>124138499</v>
       </c>
       <c r="B44" t="n">
         <v>57513</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436577</v>
+        <v>436565</v>
       </c>
       <c r="R44" t="n">
-        <v>7036686</v>
+        <v>7036491</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138500</v>
+        <v>124138492</v>
       </c>
       <c r="B45" t="n">
         <v>57513</v>
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436566</v>
+        <v>436577</v>
       </c>
       <c r="R45" t="n">
-        <v>7036478</v>
+        <v>7036686</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6055,7 +6055,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138505</v>
+        <v>124138502</v>
       </c>
       <c r="B46" t="n">
         <v>57513</v>
@@ -6089,16 +6089,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436515</v>
+        <v>436558</v>
       </c>
       <c r="R46" t="n">
-        <v>7036414</v>
+        <v>7036469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6135,7 +6143,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,7 +6170,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138502</v>
+        <v>124138500</v>
       </c>
       <c r="B47" t="n">
         <v>57513</v>
@@ -6196,24 +6204,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436558</v>
+        <v>436566</v>
       </c>
       <c r="R47" t="n">
-        <v>7036469</v>
+        <v>7036478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6277,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138489</v>
+        <v>124123983</v>
       </c>
       <c r="B48" t="n">
         <v>57513</v>
@@ -6311,16 +6311,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436553</v>
+        <v>436575</v>
       </c>
       <c r="R48" t="n">
-        <v>7036719</v>
+        <v>7036750</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6350,14 +6355,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6368,23 +6383,48 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124123983</v>
+        <v>124138497</v>
       </c>
       <c r="B49" t="n">
         <v>57513</v>
@@ -6418,21 +6458,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436575</v>
+        <v>436619</v>
       </c>
       <c r="R49" t="n">
-        <v>7036750</v>
+        <v>7036576</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6462,24 +6497,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6490,48 +6515,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138490</v>
+        <v>124138489</v>
       </c>
       <c r="B50" t="n">
         <v>57513</v>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436542</v>
+        <v>436553</v>
       </c>
       <c r="R50" t="n">
-        <v>7036748</v>
+        <v>7036719</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138497</v>
+        <v>124138505</v>
       </c>
       <c r="B51" t="n">
         <v>57513</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436619</v>
+        <v>436515</v>
       </c>
       <c r="R51" t="n">
-        <v>7036576</v>
+        <v>7036414</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138494</v>
+        <v>124138490</v>
       </c>
       <c r="B52" t="n">
         <v>57513</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436665</v>
+        <v>436542</v>
       </c>
       <c r="R52" t="n">
-        <v>7036654</v>
+        <v>7036748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138499</v>
+        <v>124138494</v>
       </c>
       <c r="B53" t="n">
         <v>57513</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436565</v>
+        <v>436665</v>
       </c>
       <c r="R53" t="n">
-        <v>7036491</v>
+        <v>7036654</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,10 +5841,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138499</v>
+        <v>124138505</v>
       </c>
       <c r="B44" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436565</v>
+        <v>436515</v>
       </c>
       <c r="R44" t="n">
-        <v>7036491</v>
+        <v>7036414</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5948,10 +5948,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138492</v>
+        <v>124138502</v>
       </c>
       <c r="B45" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5982,16 +5982,24 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436577</v>
+        <v>436558</v>
       </c>
       <c r="R45" t="n">
-        <v>7036686</v>
+        <v>7036469</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6028,7 +6036,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6055,10 +6063,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138502</v>
+        <v>124138497</v>
       </c>
       <c r="B46" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6089,24 +6097,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436558</v>
+        <v>436619</v>
       </c>
       <c r="R46" t="n">
-        <v>7036469</v>
+        <v>7036576</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>2m upp i knäckt gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6170,10 +6170,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138500</v>
+        <v>124138489</v>
       </c>
       <c r="B47" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436566</v>
+        <v>436553</v>
       </c>
       <c r="R47" t="n">
-        <v>7036478</v>
+        <v>7036719</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124123983</v>
+        <v>124138499</v>
       </c>
       <c r="B48" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6311,21 +6311,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436575</v>
+        <v>436565</v>
       </c>
       <c r="R48" t="n">
-        <v>7036750</v>
+        <v>7036491</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6355,24 +6350,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6383,51 +6368,26 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124138497</v>
+        <v>124123983</v>
       </c>
       <c r="B49" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6458,16 +6418,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436619</v>
+        <v>436575</v>
       </c>
       <c r="R49" t="n">
-        <v>7036576</v>
+        <v>7036750</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6497,14 +6462,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6515,26 +6490,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138489</v>
+        <v>124138492</v>
       </c>
       <c r="B50" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436553</v>
+        <v>436577</v>
       </c>
       <c r="R50" t="n">
-        <v>7036719</v>
+        <v>7036686</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6638,10 +6638,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138505</v>
+        <v>124138500</v>
       </c>
       <c r="B51" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436515</v>
+        <v>436566</v>
       </c>
       <c r="R51" t="n">
-        <v>7036414</v>
+        <v>7036478</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6745,10 +6745,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138490</v>
+        <v>124138494</v>
       </c>
       <c r="B52" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436542</v>
+        <v>436665</v>
       </c>
       <c r="R52" t="n">
-        <v>7036748</v>
+        <v>7036654</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,10 +6852,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138494</v>
+        <v>124138490</v>
       </c>
       <c r="B53" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436665</v>
+        <v>436542</v>
       </c>
       <c r="R53" t="n">
-        <v>7036654</v>
+        <v>7036748</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -5841,7 +5841,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138505</v>
+        <v>124123983</v>
       </c>
       <c r="B44" t="n">
         <v>57635</v>
@@ -5875,16 +5875,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436515</v>
+        <v>436575</v>
       </c>
       <c r="R44" t="n">
-        <v>7036414</v>
+        <v>7036750</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5914,14 +5919,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5932,16 +5947,41 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6170,7 +6210,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124138489</v>
+        <v>124138494</v>
       </c>
       <c r="B47" t="n">
         <v>57635</v>
@@ -6210,10 +6250,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>436553</v>
+        <v>436665</v>
       </c>
       <c r="R47" t="n">
-        <v>7036719</v>
+        <v>7036654</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6250,7 +6290,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,7 +6317,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124138499</v>
+        <v>124138505</v>
       </c>
       <c r="B48" t="n">
         <v>57635</v>
@@ -6317,10 +6357,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>436565</v>
+        <v>436515</v>
       </c>
       <c r="R48" t="n">
-        <v>7036491</v>
+        <v>7036414</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6357,7 +6397,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6384,7 +6424,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124123983</v>
+        <v>124138500</v>
       </c>
       <c r="B49" t="n">
         <v>57635</v>
@@ -6418,21 +6458,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>436575</v>
+        <v>436566</v>
       </c>
       <c r="R49" t="n">
-        <v>7036750</v>
+        <v>7036478</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6462,24 +6497,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, äldre.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6490,48 +6515,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124138492</v>
+        <v>124138499</v>
       </c>
       <c r="B50" t="n">
         <v>57635</v>
@@ -6571,10 +6571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>436577</v>
+        <v>436565</v>
       </c>
       <c r="R50" t="n">
-        <v>7036686</v>
+        <v>7036491</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6638,7 +6638,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124138500</v>
+        <v>124138489</v>
       </c>
       <c r="B51" t="n">
         <v>57635</v>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>436566</v>
+        <v>436553</v>
       </c>
       <c r="R51" t="n">
-        <v>7036478</v>
+        <v>7036719</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124138494</v>
+        <v>124138490</v>
       </c>
       <c r="B52" t="n">
         <v>57635</v>
@@ -6785,10 +6785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>436665</v>
+        <v>436542</v>
       </c>
       <c r="R52" t="n">
-        <v>7036654</v>
+        <v>7036748</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6852,7 +6852,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124138490</v>
+        <v>124138492</v>
       </c>
       <c r="B53" t="n">
         <v>57635</v>
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>436542</v>
+        <v>436577</v>
       </c>
       <c r="R53" t="n">
-        <v>7036748</v>
+        <v>7036686</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -6354,7 +6354,7 @@
         <v>124138502</v>
       </c>
       <c r="B49" t="n">
-        <v>57635</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124120678</v>
+        <v>124138517</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436489</v>
+        <v>436623</v>
       </c>
       <c r="R2" t="n">
-        <v>7036772</v>
+        <v>7036558</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,26 +743,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,56 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124138521</v>
+        <v>124124067</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,34 +783,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436548</v>
+        <v>436566</v>
       </c>
       <c r="R3" t="n">
-        <v>7036699</v>
+        <v>7036754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,11 +845,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -908,88 +868,89 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124120467</v>
+        <v>124138484</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436380</v>
+        <v>436524</v>
       </c>
       <c r="R4" t="n">
-        <v>7036719</v>
+        <v>7036571</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1016,21 +977,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1039,36 +990,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124138529</v>
+        <v>124138486</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1100,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436661</v>
+        <v>436686</v>
       </c>
       <c r="R5" t="n">
-        <v>7036719</v>
+        <v>7036815</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1165,12 +1106,7 @@
         <v>124138487</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,62 +1200,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124138508</v>
+        <v>124138516</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436630</v>
+        <v>436629</v>
       </c>
       <c r="R7" t="n">
-        <v>7036552</v>
+        <v>7036589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1378,15 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124123595</v>
+        <v>124120678</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,37 +1308,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436560</v>
+        <v>436489</v>
       </c>
       <c r="R8" t="n">
-        <v>7036869</v>
+        <v>7036772</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1382,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,22 +1406,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1515,57 +1439,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124121529</v>
+        <v>124124271</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1574,13 +1479,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436390</v>
+        <v>436563</v>
       </c>
       <c r="R9" t="n">
-        <v>7036767</v>
+        <v>7036748</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1609,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1619,12 +1524,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:46</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1639,6 +1539,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1656,58 +1576,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124123667</v>
+        <v>124119822</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436566</v>
+        <v>436287</v>
       </c>
       <c r="R10" t="n">
-        <v>7036880</v>
+        <v>7036648</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1734,26 +1644,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska och äldre hackspår i stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1780,12 +1675,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1803,58 +1698,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124120889</v>
+        <v>124119898</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436483</v>
+        <v>436282</v>
       </c>
       <c r="R11" t="n">
-        <v>7036812</v>
+        <v>7036676</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1883,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1893,12 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Hackspår i stambasen.</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,12 +1807,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1950,53 +1830,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124138514</v>
+        <v>124120544</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436467</v>
+        <v>436449</v>
       </c>
       <c r="R12" t="n">
-        <v>7036669</v>
+        <v>7036726</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2023,14 +1898,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack äldre</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,35 +1921,55 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124138531</v>
+        <v>124121014</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2093,17 +1993,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436554</v>
+        <v>436440</v>
       </c>
       <c r="R13" t="n">
-        <v>7036548</v>
+        <v>7036807</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2130,14 +2030,19 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,35 +2053,55 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124122426</v>
+        <v>124121762</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2204,13 +2129,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436497</v>
+        <v>436547</v>
       </c>
       <c r="R14" t="n">
-        <v>7036929</v>
+        <v>7036757</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2239,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2249,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,12 +2203,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2301,58 +2226,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124120741</v>
+        <v>124121853</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436483</v>
+        <v>436611</v>
       </c>
       <c r="R15" t="n">
-        <v>7036788</v>
+        <v>7036804</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2381,7 +2296,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2391,7 +2306,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2420,12 +2340,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2443,19 +2363,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124138535</v>
+        <v>124122426</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2479,17 +2394,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436609</v>
+        <v>436497</v>
       </c>
       <c r="R16" t="n">
-        <v>7036617</v>
+        <v>7036929</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2516,11 +2431,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2529,88 +2454,89 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124122092</v>
+        <v>124123595</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436572</v>
+        <v>436560</v>
       </c>
       <c r="R17" t="n">
-        <v>7036828</v>
+        <v>7036869</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,7 +2565,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,12 +2575,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,6 +2590,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2686,53 +2627,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124138517</v>
+        <v>124124670</v>
       </c>
       <c r="B18" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436623</v>
+        <v>436446</v>
       </c>
       <c r="R18" t="n">
-        <v>7036558</v>
+        <v>7036676</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2759,11 +2695,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2772,74 +2718,89 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124120703</v>
+        <v>124138531</v>
       </c>
       <c r="B19" t="n">
-        <v>79927</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436492</v>
+        <v>436554</v>
       </c>
       <c r="R19" t="n">
-        <v>7036774</v>
+        <v>7036548</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2866,24 +2827,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På en hyfsat grov gammal sälg.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2894,60 +2845,30 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124124670</v>
+        <v>124138534</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2971,17 +2892,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436446</v>
+        <v>436665</v>
       </c>
       <c r="R20" t="n">
-        <v>7036676</v>
+        <v>7036708</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3008,21 +2929,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3031,96 +2942,61 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124124271</v>
+        <v>124138535</v>
       </c>
       <c r="B21" t="n">
-        <v>91700</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436563</v>
+        <v>436609</v>
       </c>
       <c r="R21" t="n">
-        <v>7036748</v>
+        <v>7036617</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3150,21 +3026,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:07</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3173,94 +3039,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124119822</v>
+        <v>124120703</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436287</v>
+        <v>436492</v>
       </c>
       <c r="R22" t="n">
-        <v>7036648</v>
+        <v>7036774</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3287,11 +3128,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3308,22 +3164,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3341,50 +3197,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124138519</v>
+        <v>124120889</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436513</v>
+        <v>436483</v>
       </c>
       <c r="R23" t="n">
-        <v>7036741</v>
+        <v>7036812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3414,11 +3270,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3427,73 +3298,79 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124122388</v>
+        <v>124123667</v>
       </c>
       <c r="B24" t="n">
-        <v>57942</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103001</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3502,13 +3379,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436519</v>
+        <v>436566</v>
       </c>
       <c r="R24" t="n">
-        <v>7036935</v>
+        <v>7036880</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3537,7 +3414,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3547,7 +3424,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Färska och äldre hackspår i stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3562,6 +3444,26 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3579,15 +3481,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124138518</v>
+        <v>124138514</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3595,16 +3492,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3613,20 +3510,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436552</v>
+        <v>436467</v>
       </c>
       <c r="R25" t="n">
-        <v>7036703</v>
+        <v>7036669</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3659,6 +3552,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3685,15 +3583,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124138486</v>
+        <v>124123983</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3701,34 +3594,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436686</v>
+        <v>436575</v>
       </c>
       <c r="R26" t="n">
-        <v>7036815</v>
+        <v>7036750</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3758,11 +3656,26 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3771,31 +3684,51 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124138484</v>
+        <v>124138489</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3803,21 +3736,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3827,10 +3760,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436524</v>
+        <v>436553</v>
       </c>
       <c r="R27" t="n">
-        <v>7036571</v>
+        <v>7036719</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3863,6 +3796,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3889,15 +3827,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124121048</v>
+        <v>124138490</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3905,42 +3838,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436428</v>
+        <v>436542</v>
       </c>
       <c r="R28" t="n">
-        <v>7036785</v>
+        <v>7036748</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3967,19 +3895,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>09:36</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>09:36</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3990,56 +3913,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124138527</v>
+        <v>124138492</v>
       </c>
       <c r="B29" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4047,21 +3940,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4071,10 +3964,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436655</v>
+        <v>436577</v>
       </c>
       <c r="R29" t="n">
-        <v>7036737</v>
+        <v>7036686</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4107,6 +4000,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4133,15 +4031,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124138534</v>
+        <v>124138494</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4149,21 +4042,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4176,7 +4069,7 @@
         <v>436665</v>
       </c>
       <c r="R30" t="n">
-        <v>7036708</v>
+        <v>7036654</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4209,6 +4102,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4235,15 +4133,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124124067</v>
+        <v>124138497</v>
       </c>
       <c r="B31" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,39 +4144,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436566</v>
+        <v>436619</v>
       </c>
       <c r="R31" t="n">
-        <v>7036754</v>
+        <v>7036576</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4313,19 +4201,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:03</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:03</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4336,56 +4219,26 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124122815</v>
+        <v>124138499</v>
       </c>
       <c r="B32" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,16 +4246,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4411,29 +4264,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436455</v>
+        <v>436565</v>
       </c>
       <c r="R32" t="n">
-        <v>7036885</v>
+        <v>7036491</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4460,19 +4303,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>10:30</t>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4483,36 +4321,26 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124121762</v>
+        <v>124138500</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4520,37 +4348,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436547</v>
+        <v>436566</v>
       </c>
       <c r="R33" t="n">
-        <v>7036757</v>
+        <v>7036478</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4577,19 +4405,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:56</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:56</t>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4600,56 +4423,26 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124138524</v>
+        <v>124138502</v>
       </c>
       <c r="B34" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4657,34 +4450,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436539</v>
+        <v>436558</v>
       </c>
       <c r="R34" t="n">
-        <v>7036496</v>
+        <v>7036469</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4717,6 +4518,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2m upp i knäckt gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4743,32 +4549,27 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124122264</v>
+        <v>124138505</v>
       </c>
       <c r="B35" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4776,39 +4577,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
         <v>436515</v>
       </c>
       <c r="R35" t="n">
-        <v>7036863</v>
+        <v>7036414</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4840,6 +4622,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4848,36 +4635,26 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124121853</v>
+        <v>124138506</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4885,37 +4662,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>436611</v>
+        <v>436289</v>
       </c>
       <c r="R36" t="n">
-        <v>7036804</v>
+        <v>7036605</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4942,24 +4719,14 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Relativt rikligt med bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4970,78 +4737,48 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124122460</v>
+        <v>124138508</v>
       </c>
       <c r="B37" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5049,11 +4786,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5061,14 +4796,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Långmyren, Långmyren, Jmt</t>
+          <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>436516</v>
+        <v>436630</v>
       </c>
       <c r="R37" t="n">
-        <v>7036958</v>
+        <v>7036552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5098,26 +4833,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5126,68 +4846,56 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124138511</v>
+        <v>124122815</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5195,17 +4903,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>436582</v>
+        <v>436455</v>
       </c>
       <c r="R38" t="n">
-        <v>7036714</v>
+        <v>7036885</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5232,11 +4940,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5245,31 +4963,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124138522</v>
+        <v>124122388</v>
       </c>
       <c r="B39" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5277,37 +4995,56 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>103001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>436590</v>
+        <v>436519</v>
       </c>
       <c r="R39" t="n">
-        <v>7036784</v>
+        <v>7036935</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5334,11 +5071,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5347,69 +5094,88 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124138516</v>
+        <v>124120467</v>
       </c>
       <c r="B40" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1209</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>436629</v>
+        <v>436380</v>
       </c>
       <c r="R40" t="n">
-        <v>7036589</v>
+        <v>7036719</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5436,11 +5202,21 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5449,69 +5225,88 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124121014</v>
+        <v>124122264</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>436440</v>
+        <v>436515</v>
       </c>
       <c r="R41" t="n">
-        <v>7036807</v>
+        <v>7036863</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5538,21 +5333,11 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5565,26 +5350,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5602,50 +5367,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124138525</v>
+        <v>124138518</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>436632</v>
+        <v>436552</v>
       </c>
       <c r="R42" t="n">
-        <v>7036740</v>
+        <v>7036703</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5704,15 +5468,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124120544</v>
+        <v>124121529</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5720,37 +5479,56 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>436449</v>
+        <v>436390</v>
       </c>
       <c r="R43" t="n">
-        <v>7036726</v>
+        <v>7036767</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5779,7 +5557,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5789,7 +5567,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En sjungande hane i flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,26 +5587,6 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5841,10 +5604,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124138490</v>
+        <v>124122092</v>
       </c>
       <c r="B44" t="n">
-        <v>57635</v>
+        <v>58114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5852,34 +5615,53 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>436542</v>
+        <v>436572</v>
       </c>
       <c r="R44" t="n">
-        <v>7036748</v>
+        <v>7036828</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5909,14 +5691,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>En sjungande hane i lämplig häckbiotop med flerskiktad äldre granskog där det finns murkna björkhögstubbar för bohål.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5927,26 +5719,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124138500</v>
+        <v>124122460</v>
       </c>
       <c r="B45" t="n">
-        <v>57635</v>
+        <v>58114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5954,34 +5751,48 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Horsmyren, Jmt</t>
+          <t>Långmyren, Långmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>436566</v>
+        <v>436516</v>
       </c>
       <c r="R45" t="n">
-        <v>7036478</v>
+        <v>7036958</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6011,14 +5822,24 @@
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-04-16</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>I flerskiktad äldre granskog. Möjligen fanns fler talltitor kring fyndplatsen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6029,26 +5850,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124138505</v>
+        <v>124138511</v>
       </c>
       <c r="B46" t="n">
-        <v>57635</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6056,34 +5882,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Horsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>436515</v>
+        <v>436582</v>
       </c>
       <c r="R46" t="n">
-        <v>7036414</v>
+        <v>7036714</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6118,11 +5956,6 @@
           <t>2025-04-16</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6144,768 +5977,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>124138492</v>
-      </c>
-      <c r="B47" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>436577</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7036686</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>124138499</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>436565</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7036491</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>124138502</v>
-      </c>
-      <c r="B49" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>436558</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7036469</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>2m upp i knäckt gran</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>124138489</v>
-      </c>
-      <c r="B50" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>436553</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7036719</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>124123983</v>
-      </c>
-      <c r="B51" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Långmyren, Långmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>436575</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7036750</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>124138497</v>
-      </c>
-      <c r="B52" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>436619</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7036576</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>124138494</v>
-      </c>
-      <c r="B53" t="n">
-        <v>57635</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Horsmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>436665</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7036654</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56633-2024 artfynd.xlsx
+++ b/artfynd/A 56633-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124119822</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124119898</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138506</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138517</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124124067</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138486</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138487</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138516</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120678</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1929,6 +1984,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124124271</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2061,6 +2121,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2193,6 +2258,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124121014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2325,6 +2395,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124121762</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2462,6 +2537,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124121853</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2594,6 +2674,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122426</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2726,6 +2811,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123595</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2858,6 +2948,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124124670</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2960,6 +3055,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138531</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3057,6 +3157,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138534</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3154,6 +3259,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138535</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3296,6 +3406,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120703</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3438,6 +3553,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120889</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3580,6 +3700,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123667</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3682,6 +3807,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138514</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3824,6 +3954,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124123983</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3926,6 +4061,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138489</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4028,6 +4168,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138490</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4130,6 +4275,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138492</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4232,6 +4382,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138494</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4334,6 +4489,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138497</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4436,6 +4596,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138499</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4538,6 +4703,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138500</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4648,6 +4818,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138502</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4750,6 +4925,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138505</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4859,6 +5039,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138508</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4981,6 +5166,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122815</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5112,6 +5302,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122388</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5243,6 +5438,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124120467</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5364,6 +5564,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122264</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5465,6 +5670,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138518</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5601,6 +5811,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124121529</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5737,6 +5952,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122092</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5868,6 +6088,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124122460</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5977,8 +6202,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124138511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>